--- a/data/tsunami_evacuation_building/data.xlsx
+++ b/data/tsunami_evacuation_building/data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H115"/>
+  <dimension ref="A1:H114"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1285,25 +1285,25 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B35" t="str">
-        <v>34.34613667</v>
+        <v>34.34465</v>
       </c>
       <c r="C35" t="str">
-        <v>134.0478458</v>
+        <v>134.05093</v>
       </c>
       <c r="D35" t="str">
-        <v>高松東急ＲＥＩホテル</v>
+        <v>丸亀町くるりん駐車場</v>
       </c>
       <c r="E35" t="str">
-        <v>高松市兵庫町9-9</v>
+        <v>高松市大工町8-1</v>
       </c>
       <c r="F35" t="str">
-        <v>３階宴会場</v>
+        <v>２階以上</v>
       </c>
       <c r="G35" t="str">
-        <v>150</v>
+        <v>5081</v>
       </c>
       <c r="H35" t="str">
         <v>四番丁</v>
@@ -1311,25 +1311,25 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36" t="str">
-        <v>34.34465</v>
+        <v>34.34417028</v>
       </c>
       <c r="C36" t="str">
-        <v>134.05093</v>
+        <v>134.0492236</v>
       </c>
       <c r="D36" t="str">
-        <v>丸亀町くるりん駐車場</v>
+        <v>美術館</v>
       </c>
       <c r="E36" t="str">
-        <v>高松市大工町8-1</v>
+        <v>高松市紺屋町10-4</v>
       </c>
       <c r="F36" t="str">
-        <v>２階以上</v>
+        <v>３階</v>
       </c>
       <c r="G36" t="str">
-        <v>5081</v>
+        <v>350</v>
       </c>
       <c r="H36" t="str">
         <v>四番丁</v>
@@ -1337,25 +1337,25 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B37" t="str">
-        <v>34.34417028</v>
+        <v>34.34583972</v>
       </c>
       <c r="C37" t="str">
-        <v>134.0492236</v>
+        <v>134.0505317</v>
       </c>
       <c r="D37" t="str">
-        <v>美術館</v>
+        <v>高松丸亀町レッツホール，カルチャールーム</v>
       </c>
       <c r="E37" t="str">
-        <v>高松市紺屋町10-4</v>
+        <v>高松市丸亀町1-1</v>
       </c>
       <c r="F37" t="str">
-        <v>３階</v>
+        <v>高松丸亀町壱番街ビル東館４階</v>
       </c>
       <c r="G37" t="str">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="H37" t="str">
         <v>四番丁</v>
@@ -1363,25 +1363,25 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" t="str">
-        <v>34.34583972</v>
+        <v>34.34155667</v>
       </c>
       <c r="C38" t="str">
-        <v>134.0505317</v>
+        <v>134.0487486</v>
       </c>
       <c r="D38" t="str">
-        <v>高松丸亀町レッツホール，カルチャールーム</v>
+        <v>丸亀町まるい亀さん</v>
       </c>
       <c r="E38" t="str">
-        <v>高松市丸亀町1-1</v>
+        <v>高松市亀井町1-2</v>
       </c>
       <c r="F38" t="str">
-        <v>高松丸亀町壱番街ビル東館４階</v>
+        <v>２階以上</v>
       </c>
       <c r="G38" t="str">
-        <v>150</v>
+        <v>3200</v>
       </c>
       <c r="H38" t="str">
         <v>四番丁</v>
@@ -1389,25 +1389,25 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" t="str">
-        <v>34.34155667</v>
+        <v>34.34347028</v>
       </c>
       <c r="C39" t="str">
-        <v>134.0487486</v>
+        <v>134.0463461</v>
       </c>
       <c r="D39" t="str">
-        <v>丸亀町まるい亀さん</v>
+        <v>四番丁小学校跡施設南北棟</v>
       </c>
       <c r="E39" t="str">
-        <v>高松市亀井町1-2</v>
+        <v>高松市番町一丁目5-1</v>
       </c>
       <c r="F39" t="str">
         <v>２階以上</v>
       </c>
       <c r="G39" t="str">
-        <v>3200</v>
+        <v>100</v>
       </c>
       <c r="H39" t="str">
         <v>四番丁</v>
@@ -1415,22 +1415,22 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40" t="str">
-        <v>34.34347028</v>
+        <v>34.34372306</v>
       </c>
       <c r="C40" t="str">
-        <v>134.0463461</v>
+        <v>134.0444686</v>
       </c>
       <c r="D40" t="str">
-        <v>四番丁小学校跡施設南北棟</v>
+        <v>四番丁コミュニティセンター</v>
       </c>
       <c r="E40" t="str">
-        <v>高松市番町一丁目5-1</v>
+        <v>高松市番町二丁目3-5</v>
       </c>
       <c r="F40" t="str">
-        <v>２階以上</v>
+        <v>２階</v>
       </c>
       <c r="G40" t="str">
         <v>100</v>
@@ -1441,25 +1441,25 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" t="str">
-        <v>34.34372306</v>
+        <v>34.34442306</v>
       </c>
       <c r="C41" t="str">
-        <v>134.0444686</v>
+        <v>134.0421797</v>
       </c>
       <c r="D41" t="str">
-        <v>四番丁コミュニティセンター</v>
+        <v>高松工芸高等学校</v>
       </c>
       <c r="E41" t="str">
-        <v>高松市番町二丁目3-5</v>
+        <v>高松市番町二丁目9-30</v>
       </c>
       <c r="F41" t="str">
-        <v>２階</v>
+        <v>体育館　２階</v>
       </c>
       <c r="G41" t="str">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H41" t="str">
         <v>四番丁</v>
@@ -1467,19 +1467,19 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42" t="str">
-        <v>34.34442306</v>
+        <v>34.34201222</v>
       </c>
       <c r="C42" t="str">
-        <v>134.0421797</v>
+        <v>134.0438575</v>
       </c>
       <c r="D42" t="str">
-        <v>高松工芸高等学校</v>
+        <v>高松高等学校</v>
       </c>
       <c r="E42" t="str">
-        <v>高松市番町二丁目9-30</v>
+        <v>高松市番町三丁目1-1</v>
       </c>
       <c r="F42" t="str">
         <v>体育館　２階</v>
@@ -1493,51 +1493,51 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43" t="str">
-        <v>34.34201222</v>
+        <v>34.34458667</v>
       </c>
       <c r="C43" t="str">
-        <v>134.0438575</v>
+        <v>134.0359136</v>
       </c>
       <c r="D43" t="str">
-        <v>高松高等学校</v>
+        <v>二番丁コミュニティセンター</v>
       </c>
       <c r="E43" t="str">
-        <v>高松市番町三丁目1-1</v>
+        <v>高松市扇町二丁目8-7</v>
       </c>
       <c r="F43" t="str">
-        <v>体育館　２階</v>
+        <v>２階</v>
       </c>
       <c r="G43" t="str">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="H43" t="str">
-        <v>四番丁</v>
+        <v>二番丁</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44" t="str">
-        <v>34.34458667</v>
+        <v>34.3482975</v>
       </c>
       <c r="C44" t="str">
-        <v>134.0359136</v>
+        <v>134.0440961</v>
       </c>
       <c r="D44" t="str">
-        <v>二番丁コミュニティセンター</v>
+        <v>高松センチュリーホテル</v>
       </c>
       <c r="E44" t="str">
-        <v>高松市扇町二丁目8-7</v>
+        <v>高松市錦町一丁目4-19</v>
       </c>
       <c r="F44" t="str">
-        <v>２階</v>
+        <v>本館屋上</v>
       </c>
       <c r="G44" t="str">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H44" t="str">
         <v>二番丁</v>
@@ -1545,25 +1545,25 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B45" t="str">
-        <v>34.3482975</v>
+        <v>34.34594222</v>
       </c>
       <c r="C45" t="str">
-        <v>134.0440961</v>
+        <v>134.0405436</v>
       </c>
       <c r="D45" t="str">
-        <v>高松センチュリーホテル</v>
+        <v>新番丁小学校</v>
       </c>
       <c r="E45" t="str">
-        <v>高松市錦町一丁目4-19</v>
+        <v>高松市錦町二丁目14-1</v>
       </c>
       <c r="F45" t="str">
-        <v>本館屋上</v>
+        <v>校舎</v>
       </c>
       <c r="G45" t="str">
-        <v>200</v>
+        <v>750</v>
       </c>
       <c r="H45" t="str">
         <v>二番丁</v>
@@ -1571,25 +1571,25 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B46" t="str">
-        <v>34.34594222</v>
+        <v>34.35111111</v>
       </c>
       <c r="C46" t="str">
-        <v>134.0405436</v>
+        <v>134.0469903</v>
       </c>
       <c r="D46" t="str">
-        <v>新番丁小学校</v>
+        <v>JRホテルクレメント高松</v>
       </c>
       <c r="E46" t="str">
-        <v>高松市錦町二丁目14-1</v>
+        <v>高松市浜ノ町1-1</v>
       </c>
       <c r="F46" t="str">
-        <v>校舎</v>
+        <v>２階共用廊下・３階宴会ロビー</v>
       </c>
       <c r="G46" t="str">
-        <v>750</v>
+        <v>850</v>
       </c>
       <c r="H46" t="str">
         <v>二番丁</v>
@@ -1597,25 +1597,25 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B47" t="str">
-        <v>34.35111111</v>
+        <v>34.34975583</v>
       </c>
       <c r="C47" t="str">
-        <v>134.0469903</v>
+        <v>134.0423183</v>
       </c>
       <c r="D47" t="str">
-        <v>JRホテルクレメント高松</v>
+        <v>四国旅客鉄道株式会社本社ビル</v>
       </c>
       <c r="E47" t="str">
-        <v>高松市浜ノ町1-1</v>
+        <v>高松市浜ノ町8-33</v>
       </c>
       <c r="F47" t="str">
-        <v>２階共用廊下・３階宴会ロビー</v>
+        <v>８階と屋上</v>
       </c>
       <c r="G47" t="str">
-        <v>850</v>
+        <v>500</v>
       </c>
       <c r="H47" t="str">
         <v>二番丁</v>
@@ -1623,25 +1623,25 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B48" t="str">
-        <v>34.34975583</v>
+        <v>34.35166</v>
       </c>
       <c r="C48" t="str">
-        <v>134.0423183</v>
+        <v>134.03847</v>
       </c>
       <c r="D48" t="str">
-        <v>四国旅客鉄道株式会社本社ビル</v>
+        <v>ロイヤルガーデン高松駅西オーシャンビュー壱番館</v>
       </c>
       <c r="E48" t="str">
-        <v>高松市浜ノ町8-33</v>
+        <v>高松市浜ノ町265番3</v>
       </c>
       <c r="F48" t="str">
-        <v>８階と屋上</v>
+        <v>各階%2525252525282～14階）の廊下及び屋上供用部分</v>
       </c>
       <c r="G48" t="str">
-        <v>500</v>
+        <v>282</v>
       </c>
       <c r="H48" t="str">
         <v>二番丁</v>
@@ -1649,25 +1649,25 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B49" t="str">
-        <v>34.35166</v>
+        <v>34.3516</v>
       </c>
       <c r="C49" t="str">
-        <v>134.03847</v>
+        <v>134.038</v>
       </c>
       <c r="D49" t="str">
-        <v>ロイヤルガーデン高松駅西オーシャンビュー壱番館</v>
+        <v>ロイヤルガーデン高松駅西オーシャンビュー弐番館</v>
       </c>
       <c r="E49" t="str">
-        <v>高松市浜ノ町265番3</v>
+        <v>高松市浜ノ町265番8</v>
       </c>
       <c r="F49" t="str">
         <v>各階%2525252525282～14階）の廊下及び屋上供用部分</v>
       </c>
       <c r="G49" t="str">
-        <v>282</v>
+        <v>230</v>
       </c>
       <c r="H49" t="str">
         <v>二番丁</v>
@@ -1675,25 +1675,25 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B50" t="str">
-        <v>34.3516</v>
+        <v>34.34388944</v>
       </c>
       <c r="C50" t="str">
-        <v>134.038</v>
+        <v>134.0340167</v>
       </c>
       <c r="D50" t="str">
-        <v>ロイヤルガーデン高松駅西オーシャンビュー弐番館</v>
+        <v>中央図書館（サンクリスタル高松）</v>
       </c>
       <c r="E50" t="str">
-        <v>高松市浜ノ町265番8</v>
+        <v>高松市昭和町一丁目2-20</v>
       </c>
       <c r="F50" t="str">
-        <v>各階%2525252525282～14階）の廊下及び屋上供用部分</v>
+        <v>３階</v>
       </c>
       <c r="G50" t="str">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="H50" t="str">
         <v>二番丁</v>
@@ -1701,25 +1701,25 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B51" t="str">
-        <v>34.34388944</v>
+        <v>34.35300278</v>
       </c>
       <c r="C51" t="str">
-        <v>134.0340167</v>
+        <v>134.0479178</v>
       </c>
       <c r="D51" t="str">
-        <v>中央図書館（サンクリスタル高松）</v>
+        <v>高松港旅客ターミナルビル</v>
       </c>
       <c r="E51" t="str">
-        <v>高松市昭和町一丁目2-20</v>
+        <v>高松市サンポート1-1</v>
       </c>
       <c r="F51" t="str">
-        <v>３階</v>
+        <v>２階</v>
       </c>
       <c r="G51" t="str">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="H51" t="str">
         <v>二番丁</v>
@@ -1727,25 +1727,25 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B52" t="str">
-        <v>34.35300278</v>
+        <v>34.352575</v>
       </c>
       <c r="C52" t="str">
-        <v>134.0479178</v>
+        <v>134.0470042</v>
       </c>
       <c r="D52" t="str">
-        <v>高松港旅客ターミナルビル</v>
+        <v>高松シンボルタワー　サンポートホール高松</v>
       </c>
       <c r="E52" t="str">
-        <v>高松市サンポート1-1</v>
+        <v>高松市サンポート2-1</v>
       </c>
       <c r="F52" t="str">
-        <v>２階</v>
+        <v>ロビー</v>
       </c>
       <c r="G52" t="str">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H52" t="str">
         <v>二番丁</v>
@@ -1753,7 +1753,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B53" t="str">
         <v>34.352575</v>
@@ -1762,16 +1762,16 @@
         <v>134.0470042</v>
       </c>
       <c r="D53" t="str">
-        <v>高松シンボルタワー　サンポートホール高松</v>
+        <v>高松シンボルタワー　かがわプラザ</v>
       </c>
       <c r="E53" t="str">
         <v>高松市サンポート2-1</v>
       </c>
       <c r="F53" t="str">
-        <v>ロビー</v>
+        <v>インフォメーションゾーン</v>
       </c>
       <c r="G53" t="str">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="H53" t="str">
         <v>二番丁</v>
@@ -1779,7 +1779,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B54" t="str">
         <v>34.352575</v>
@@ -1788,16 +1788,16 @@
         <v>134.0470042</v>
       </c>
       <c r="D54" t="str">
-        <v>高松シンボルタワー　かがわプラザ</v>
+        <v>高松シンボルタワー　共用部</v>
       </c>
       <c r="E54" t="str">
         <v>高松市サンポート2-1</v>
       </c>
       <c r="F54" t="str">
-        <v>インフォメーションゾーン</v>
+        <v>３階・４階・７階・８階の一部</v>
       </c>
       <c r="G54" t="str">
-        <v>250</v>
+        <v>1500</v>
       </c>
       <c r="H54" t="str">
         <v>二番丁</v>
@@ -1805,51 +1805,51 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B55" t="str">
-        <v>34.352575</v>
+        <v>34.3471725</v>
       </c>
       <c r="C55" t="str">
-        <v>134.0470042</v>
+        <v>134.0301975</v>
       </c>
       <c r="D55" t="str">
-        <v>高松シンボルタワー　共用部</v>
+        <v>日新小学校跡施設</v>
       </c>
       <c r="E55" t="str">
-        <v>高松市サンポート2-1</v>
+        <v>高松市瀬戸内町18-2</v>
       </c>
       <c r="F55" t="str">
-        <v>３階・４階・７階・８階の一部</v>
+        <v>体育館</v>
       </c>
       <c r="G55" t="str">
-        <v>1500</v>
+        <v>400</v>
       </c>
       <c r="H55" t="str">
-        <v>二番丁</v>
+        <v>日新</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B56" t="str">
-        <v>34.3471725</v>
+        <v>34.34767528</v>
       </c>
       <c r="C56" t="str">
-        <v>134.0301975</v>
+        <v>134.0326083</v>
       </c>
       <c r="D56" t="str">
-        <v>日新小学校跡施設</v>
+        <v>日新コミュニティセンター</v>
       </c>
       <c r="E56" t="str">
-        <v>高松市瀬戸内町18-2</v>
+        <v>高松市瀬戸内町22-9</v>
       </c>
       <c r="F56" t="str">
-        <v>体育館</v>
+        <v>２階</v>
       </c>
       <c r="G56" t="str">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H56" t="str">
         <v>日新</v>
@@ -1857,51 +1857,51 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B57" t="str">
-        <v>34.34767528</v>
+        <v>34.33778472</v>
       </c>
       <c r="C57" t="str">
-        <v>134.0326083</v>
+        <v>134.0400219</v>
       </c>
       <c r="D57" t="str">
-        <v>日新コミュニティセンター</v>
+        <v>亀阜小学校</v>
       </c>
       <c r="E57" t="str">
-        <v>高松市瀬戸内町22-9</v>
+        <v>高松市亀岡町10-1</v>
       </c>
       <c r="F57" t="str">
-        <v>２階</v>
+        <v>校舎</v>
       </c>
       <c r="G57" t="str">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H57" t="str">
-        <v>日新</v>
+        <v>亀阜</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B58" t="str">
-        <v>34.33778472</v>
+        <v>34.33931222</v>
       </c>
       <c r="C58" t="str">
-        <v>134.0400219</v>
+        <v>134.0354667</v>
       </c>
       <c r="D58" t="str">
-        <v>亀阜小学校</v>
+        <v>亀阜コミュニティセンター</v>
       </c>
       <c r="E58" t="str">
-        <v>高松市亀岡町10-1</v>
+        <v>高松市宮脇町一丁目6-18</v>
       </c>
       <c r="F58" t="str">
-        <v>校舎</v>
+        <v>２階</v>
       </c>
       <c r="G58" t="str">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="H58" t="str">
         <v>亀阜</v>
@@ -1909,25 +1909,25 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B59" t="str">
-        <v>34.33931222</v>
+        <v>34.34047583</v>
       </c>
       <c r="C59" t="str">
-        <v>134.0354667</v>
+        <v>134.0301781</v>
       </c>
       <c r="D59" t="str">
-        <v>亀阜コミュニティセンター</v>
+        <v>香川県教育会館（ミューズホール）</v>
       </c>
       <c r="E59" t="str">
-        <v>高松市宮脇町一丁目6-18</v>
+        <v>高松市西宝町二丁目6-40</v>
       </c>
       <c r="F59" t="str">
-        <v>２階</v>
+        <v>２階・３階・５階・６階の会議室</v>
       </c>
       <c r="G59" t="str">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="H59" t="str">
         <v>亀阜</v>
@@ -1935,22 +1935,22 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B60" t="str">
-        <v>34.34047583</v>
+        <v>34.342945</v>
       </c>
       <c r="C60" t="str">
-        <v>134.0301781</v>
+        <v>134.0261256</v>
       </c>
       <c r="D60" t="str">
-        <v>香川県教育会館（ミューズホール）</v>
+        <v>喜代美山荘　花樹海</v>
       </c>
       <c r="E60" t="str">
-        <v>高松市西宝町二丁目6-40</v>
+        <v>高松市西宝町三丁目5-10</v>
       </c>
       <c r="F60" t="str">
-        <v>２階・３階・５階・６階の会議室</v>
+        <v>１階ロビー</v>
       </c>
       <c r="G60" t="str">
         <v>400</v>
@@ -1961,25 +1961,25 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B61" t="str">
-        <v>34.342945</v>
+        <v>34.34042333</v>
       </c>
       <c r="C61" t="str">
-        <v>134.0261256</v>
+        <v>134.0337861</v>
       </c>
       <c r="D61" t="str">
-        <v>喜代美山荘　花樹海</v>
+        <v>紫雲中学校</v>
       </c>
       <c r="E61" t="str">
-        <v>高松市西宝町三丁目5-10</v>
+        <v>高松市紫雲町8-25</v>
       </c>
       <c r="F61" t="str">
-        <v>１階ロビー</v>
+        <v>校舎</v>
       </c>
       <c r="G61" t="str">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="H61" t="str">
         <v>亀阜</v>
@@ -1987,25 +1987,25 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B62" t="str">
-        <v>34.34042333</v>
+        <v>34.343799</v>
       </c>
       <c r="C62" t="str">
-        <v>134.0337861</v>
+        <v>134.02003</v>
       </c>
       <c r="D62" t="str">
-        <v>紫雲中学校</v>
+        <v>アナザースタイル</v>
       </c>
       <c r="E62" t="str">
-        <v>高松市紫雲町8-25</v>
+        <v>高松市西宝町3丁目670番地</v>
       </c>
       <c r="F62" t="str">
-        <v>校舎</v>
+        <v>1階</v>
       </c>
       <c r="G62" t="str">
-        <v>1000</v>
+        <v>119</v>
       </c>
       <c r="H62" t="str">
         <v>亀阜</v>
@@ -2013,48 +2013,48 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B63" t="str">
-        <v>34.343799</v>
+        <v>34.319237</v>
       </c>
       <c r="C63" t="str">
-        <v>134.02003</v>
+        <v>134.076215</v>
       </c>
       <c r="D63" t="str">
-        <v>アナザースタイル</v>
+        <v>木太南コミュニティセンター</v>
       </c>
       <c r="E63" t="str">
-        <v>高松市西宝町3丁目670番地</v>
+        <v>高松市木太町1486</v>
       </c>
       <c r="F63" t="str">
-        <v>1階</v>
+        <v>２階</v>
       </c>
       <c r="G63" t="str">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="H63" t="str">
-        <v>亀阜</v>
+        <v>木太</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B64" t="str">
-        <v>34.319237</v>
+        <v>34.32080417</v>
       </c>
       <c r="C64" t="str">
-        <v>134.076215</v>
+        <v>134.0747194</v>
       </c>
       <c r="D64" t="str">
-        <v>木太南コミュニティセンター</v>
+        <v>木太南小学校</v>
       </c>
       <c r="E64" t="str">
-        <v>高松市木太町1486</v>
+        <v>高松市木太町1530-1</v>
       </c>
       <c r="F64" t="str">
-        <v>２階</v>
+        <v>校舎</v>
       </c>
       <c r="G64" t="str">
         <v>50</v>
@@ -2065,25 +2065,25 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B65" t="str">
-        <v>34.32080417</v>
+        <v>34.32491472</v>
       </c>
       <c r="C65" t="str">
-        <v>134.0747194</v>
+        <v>134.0698392</v>
       </c>
       <c r="D65" t="str">
-        <v>木太南小学校</v>
+        <v>香川県農業協同組合木太支店</v>
       </c>
       <c r="E65" t="str">
-        <v>高松市木太町1530-1</v>
+        <v>高松市木太町1669</v>
       </c>
       <c r="F65" t="str">
-        <v>校舎</v>
+        <v>２階</v>
       </c>
       <c r="G65" t="str">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="H65" t="str">
         <v>木太</v>
@@ -2091,25 +2091,25 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B66" t="str">
-        <v>34.32491472</v>
+        <v>34.3336525</v>
       </c>
       <c r="C66" t="str">
-        <v>134.0698392</v>
+        <v>134.0709525</v>
       </c>
       <c r="D66" t="str">
-        <v>香川県農業協同組合木太支店</v>
+        <v>高松国際ホテル</v>
       </c>
       <c r="E66" t="str">
-        <v>高松市木太町1669</v>
+        <v>高松市木太町2191-1</v>
       </c>
       <c r="F66" t="str">
-        <v>２階</v>
+        <v>宴会棟の３階</v>
       </c>
       <c r="G66" t="str">
-        <v>300</v>
+        <v>1050</v>
       </c>
       <c r="H66" t="str">
         <v>木太</v>
@@ -2117,25 +2117,25 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B67" t="str">
-        <v>34.3336525</v>
+        <v>34.3389075</v>
       </c>
       <c r="C67" t="str">
-        <v>134.0709525</v>
+        <v>134.0721661</v>
       </c>
       <c r="D67" t="str">
-        <v>高松国際ホテル</v>
+        <v>環境業務センター</v>
       </c>
       <c r="E67" t="str">
-        <v>高松市木太町2191-1</v>
+        <v>高松市木太町2282-1</v>
       </c>
       <c r="F67" t="str">
-        <v>宴会棟の３階</v>
+        <v>４階</v>
       </c>
       <c r="G67" t="str">
-        <v>1050</v>
+        <v>450</v>
       </c>
       <c r="H67" t="str">
         <v>木太</v>
@@ -2143,25 +2143,25 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B68" t="str">
-        <v>34.3389075</v>
+        <v>34.32491472</v>
       </c>
       <c r="C68" t="str">
-        <v>134.0721661</v>
+        <v>134.0698392</v>
       </c>
       <c r="D68" t="str">
-        <v>環境業務センター</v>
+        <v>マルハン高松店</v>
       </c>
       <c r="E68" t="str">
-        <v>高松市木太町2282-1</v>
+        <v>高松市木太町2425</v>
       </c>
       <c r="F68" t="str">
-        <v>４階</v>
+        <v>立体駐車場の２階以上</v>
       </c>
       <c r="G68" t="str">
-        <v>450</v>
+        <v>6350</v>
       </c>
       <c r="H68" t="str">
         <v>木太</v>
@@ -2169,7 +2169,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B69" t="str">
         <v>34.32491472</v>
@@ -2178,16 +2178,16 @@
         <v>134.0698392</v>
       </c>
       <c r="D69" t="str">
-        <v>マルハン高松店</v>
+        <v>木太北部コミュニティセンター</v>
       </c>
       <c r="E69" t="str">
-        <v>高松市木太町2425</v>
+        <v>高松市木太町2603</v>
       </c>
       <c r="F69" t="str">
-        <v>立体駐車場の２階以上</v>
+        <v>２階</v>
       </c>
       <c r="G69" t="str">
-        <v>6350</v>
+        <v>50</v>
       </c>
       <c r="H69" t="str">
         <v>木太</v>
@@ -2195,7 +2195,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B70" t="str">
         <v>34.32491472</v>
@@ -2204,16 +2204,16 @@
         <v>134.0698392</v>
       </c>
       <c r="D70" t="str">
-        <v>木太北部コミュニティセンター</v>
+        <v>木太北部小学校</v>
       </c>
       <c r="E70" t="str">
-        <v>高松市木太町2603</v>
+        <v>高松市木太町2613</v>
       </c>
       <c r="F70" t="str">
-        <v>２階</v>
+        <v>校舎</v>
       </c>
       <c r="G70" t="str">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="H70" t="str">
         <v>木太</v>
@@ -2221,7 +2221,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B71" t="str">
         <v>34.32491472</v>
@@ -2230,16 +2230,16 @@
         <v>134.0698392</v>
       </c>
       <c r="D71" t="str">
-        <v>木太北部小学校</v>
+        <v>木太小学校</v>
       </c>
       <c r="E71" t="str">
-        <v>高松市木太町2613</v>
+        <v>高松市木太町3480</v>
       </c>
       <c r="F71" t="str">
         <v>校舎</v>
       </c>
       <c r="G71" t="str">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="H71" t="str">
         <v>木太</v>
@@ -2247,7 +2247,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B72" t="str">
         <v>34.32491472</v>
@@ -2256,13 +2256,13 @@
         <v>134.0698392</v>
       </c>
       <c r="D72" t="str">
-        <v>木太小学校</v>
+        <v>特別養護老人ホーム法寿苑</v>
       </c>
       <c r="E72" t="str">
-        <v>高松市木太町3480</v>
+        <v>高松市木太町3308</v>
       </c>
       <c r="F72" t="str">
-        <v>校舎</v>
+        <v>３階レクリエーションルーム・３階地域交流ルーム</v>
       </c>
       <c r="G72" t="str">
         <v>200</v>
@@ -2273,25 +2273,25 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B73" t="str">
-        <v>34.32491472</v>
+        <v xml:space="preserve">34.329139 </v>
       </c>
       <c r="C73" t="str">
-        <v>134.0698392</v>
+        <v>134.071112</v>
       </c>
       <c r="D73" t="str">
-        <v>特別養護老人ホーム法寿苑</v>
+        <v>四国財務局合同宿舎深田住宅</v>
       </c>
       <c r="E73" t="str">
-        <v>高松市木太町3308</v>
+        <v>高松市木太町1992</v>
       </c>
       <c r="F73" t="str">
-        <v>３階レクリエーションルーム・３階地域交流ルーム</v>
+        <v>３階・４階・５階の廊下</v>
       </c>
       <c r="G73" t="str">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H73" t="str">
         <v>木太</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B74" t="str">
-        <v xml:space="preserve">34.329139 </v>
+        <v>34.326186</v>
       </c>
       <c r="C74" t="str">
-        <v>134.071112</v>
+        <v>134.076753</v>
       </c>
       <c r="D74" t="str">
-        <v>四国財務局合同宿舎深田住宅</v>
+        <v>木太コミュニティセンター</v>
       </c>
       <c r="E74" t="str">
-        <v>高松市木太町1992</v>
+        <v>高松市木太町3480-2</v>
       </c>
       <c r="F74" t="str">
-        <v>３階・４階・５階の廊下</v>
+        <v>2階</v>
       </c>
       <c r="G74" t="str">
         <v>150</v>
@@ -2325,51 +2325,51 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B75" t="str">
-        <v>34.326186</v>
+        <v>34.3537625</v>
       </c>
       <c r="C75" t="str">
-        <v>134.076753</v>
+        <v>134.1159869</v>
       </c>
       <c r="D75" t="str">
-        <v>木太コミュニティセンター</v>
+        <v>屋島東小学校</v>
       </c>
       <c r="E75" t="str">
-        <v>高松市木太町3480-2</v>
+        <v>高松市屋島東町942-1</v>
       </c>
       <c r="F75" t="str">
-        <v>2階</v>
+        <v>体育館</v>
       </c>
       <c r="G75" t="str">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H75" t="str">
-        <v>木太</v>
+        <v>屋島</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B76" t="str">
-        <v>34.3537625</v>
+        <v>34.34742667</v>
       </c>
       <c r="C76" t="str">
-        <v>134.1159869</v>
+        <v>134.1031936</v>
       </c>
       <c r="D76" t="str">
-        <v>屋島東小学校</v>
+        <v>屋島中学校</v>
       </c>
       <c r="E76" t="str">
-        <v>高松市屋島東町942-1</v>
+        <v>高松市屋島中町295</v>
       </c>
       <c r="F76" t="str">
-        <v>体育館</v>
+        <v>校舎</v>
       </c>
       <c r="G76" t="str">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="H76" t="str">
         <v>屋島</v>
@@ -2377,25 +2377,25 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B77" t="str">
-        <v>34.34742667</v>
+        <v>34.347035</v>
       </c>
       <c r="C77" t="str">
-        <v>134.1031936</v>
+        <v>134.0996331</v>
       </c>
       <c r="D77" t="str">
-        <v>屋島中学校</v>
+        <v>屋島小学校</v>
       </c>
       <c r="E77" t="str">
-        <v>高松市屋島中町295</v>
+        <v>高松市屋島西町1205-1</v>
       </c>
       <c r="F77" t="str">
-        <v>校舎</v>
+        <v>体育館</v>
       </c>
       <c r="G77" t="str">
-        <v>100</v>
+        <v>650</v>
       </c>
       <c r="H77" t="str">
         <v>屋島</v>
@@ -2403,25 +2403,25 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B78" t="str">
-        <v>34.347035</v>
+        <v>34.36114722</v>
       </c>
       <c r="C78" t="str">
-        <v>134.0996331</v>
+        <v>134.0943553</v>
       </c>
       <c r="D78" t="str">
-        <v>屋島小学校</v>
+        <v>株式会社マルナカ　パワーシティ屋島</v>
       </c>
       <c r="E78" t="str">
-        <v>高松市屋島西町1205-1</v>
+        <v>高松市屋島西町1907-1</v>
       </c>
       <c r="F78" t="str">
-        <v>体育館</v>
+        <v>立体駐車場の２階・３階</v>
       </c>
       <c r="G78" t="str">
-        <v>650</v>
+        <v>2850</v>
       </c>
       <c r="H78" t="str">
         <v>屋島</v>
@@ -2429,25 +2429,25 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B79" t="str">
-        <v>34.36114722</v>
+        <v>34.34418222</v>
       </c>
       <c r="C79" t="str">
-        <v>134.0943553</v>
+        <v>134.0881619</v>
       </c>
       <c r="D79" t="str">
-        <v>株式会社マルナカ　パワーシティ屋島</v>
+        <v>西村ジョイ屋島店</v>
       </c>
       <c r="E79" t="str">
-        <v>高松市屋島西町1907-1</v>
+        <v>高松市屋島西町2105-8</v>
       </c>
       <c r="F79" t="str">
-        <v>立体駐車場の２階・３階</v>
+        <v>立体駐車場の２階と屋上</v>
       </c>
       <c r="G79" t="str">
-        <v>2850</v>
+        <v>8000</v>
       </c>
       <c r="H79" t="str">
         <v>屋島</v>
@@ -2455,25 +2455,25 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B80" t="str">
-        <v>34.34418222</v>
+        <v>34.35843639</v>
       </c>
       <c r="C80" t="str">
-        <v>134.0881619</v>
+        <v>134.0893058</v>
       </c>
       <c r="D80" t="str">
-        <v>西村ジョイ屋島店</v>
+        <v>社会福祉法人楽生会ケアハウス屋島</v>
       </c>
       <c r="E80" t="str">
-        <v>高松市屋島西町2105-8</v>
+        <v>高松市屋島西町2277-1</v>
       </c>
       <c r="F80" t="str">
-        <v>立体駐車場の２階と屋上</v>
+        <v>５階</v>
       </c>
       <c r="G80" t="str">
-        <v>8000</v>
+        <v>450</v>
       </c>
       <c r="H80" t="str">
         <v>屋島</v>
@@ -2481,25 +2481,25 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B81" t="str">
-        <v>34.35843639</v>
+        <v>34.34645269</v>
       </c>
       <c r="C81" t="str">
-        <v>134.0893058</v>
+        <v>134.0859116</v>
       </c>
       <c r="D81" t="str">
-        <v>社会福祉法人楽生会ケアハウス屋島</v>
+        <v>せとうち観光専門職短期大学</v>
       </c>
       <c r="E81" t="str">
-        <v>高松市屋島西町2277-1</v>
+        <v>高松市屋島西町2366-1</v>
       </c>
       <c r="F81" t="str">
-        <v>５階</v>
+        <v>２階から４階まで</v>
       </c>
       <c r="G81" t="str">
-        <v>450</v>
+        <v>2500</v>
       </c>
       <c r="H81" t="str">
         <v>屋島</v>
@@ -2507,25 +2507,25 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B82" t="str">
-        <v>34.34645269</v>
+        <v>34.36114722</v>
       </c>
       <c r="C82" t="str">
-        <v>134.0859116</v>
+        <v>134.0943553</v>
       </c>
       <c r="D82" t="str">
-        <v>せとうち観光専門職短期大学</v>
+        <v>屋島西小学校</v>
       </c>
       <c r="E82" t="str">
-        <v>高松市屋島西町2366-1</v>
+        <v>高松市屋島西町2469</v>
       </c>
       <c r="F82" t="str">
-        <v>２階から４階まで</v>
+        <v>校舎</v>
       </c>
       <c r="G82" t="str">
-        <v>2500</v>
+        <v>200</v>
       </c>
       <c r="H82" t="str">
         <v>屋島</v>
@@ -2533,25 +2533,25 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B83" t="str">
-        <v>34.36114722</v>
+        <v>34.35227583</v>
       </c>
       <c r="C83" t="str">
-        <v>134.0943553</v>
+        <v>134.0891614</v>
       </c>
       <c r="D83" t="str">
-        <v>屋島西小学校</v>
+        <v>屋島西コミュニティセンター</v>
       </c>
       <c r="E83" t="str">
-        <v>高松市屋島西町2469</v>
+        <v>高松市屋島西町2483-2</v>
       </c>
       <c r="F83" t="str">
-        <v>校舎</v>
+        <v>２階</v>
       </c>
       <c r="G83" t="str">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="H83" t="str">
         <v>屋島</v>
@@ -2559,25 +2559,25 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B84" t="str">
-        <v>34.35227583</v>
+        <v>34.35927806</v>
       </c>
       <c r="C84" t="str">
-        <v>134.0891614</v>
+        <v>134.10301</v>
       </c>
       <c r="D84" t="str">
-        <v>屋島西コミュニティセンター</v>
+        <v>屋島東コミュニティセンター</v>
       </c>
       <c r="E84" t="str">
-        <v>高松市屋島西町2483-2</v>
+        <v>高松市屋島東町928</v>
       </c>
       <c r="F84" t="str">
-        <v>２階</v>
+        <v>１階・２階</v>
       </c>
       <c r="G84" t="str">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H84" t="str">
         <v>屋島</v>
@@ -2585,25 +2585,25 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B85" t="str">
-        <v>34.35927806</v>
+        <v>34.36114722</v>
       </c>
       <c r="C85" t="str">
-        <v>134.10301</v>
+        <v>134.0943553</v>
       </c>
       <c r="D85" t="str">
-        <v>屋島東コミュニティセンター</v>
+        <v>四国財務局合同宿舎屋島住宅　　　　　　　　　１号棟，２号棟</v>
       </c>
       <c r="E85" t="str">
-        <v>高松市屋島東町928</v>
+        <v>高松市屋島西町1403</v>
       </c>
       <c r="F85" t="str">
-        <v>１階・２階</v>
+        <v>３階から６階の廊下部分</v>
       </c>
       <c r="G85" t="str">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="H85" t="str">
         <v>屋島</v>
@@ -2611,51 +2611,51 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B86" t="str">
-        <v>34.36114722</v>
+        <v>34.32964</v>
       </c>
       <c r="C86" t="str">
-        <v>134.0943553</v>
+        <v>134.087006</v>
       </c>
       <c r="D86" t="str">
-        <v>四国財務局合同宿舎屋島住宅　　　　　　　　　１号棟，２号棟</v>
+        <v>高松大学・高松短期大学</v>
       </c>
       <c r="E86" t="str">
-        <v>高松市屋島西町1403</v>
+        <v>高松市春日町960</v>
       </c>
       <c r="F86" t="str">
-        <v>３階から６階の廊下部分</v>
+        <v>本館の２，３，４，５階 ・ 1号館２，３，４階 ・ ２号館の２，３階 ・ 図書館の３階 ・ 学生会館の２階 ・ クラブハウスの２階 ・ 体育館の２階</v>
       </c>
       <c r="G86" t="str">
-        <v>1100</v>
+        <v>2750</v>
       </c>
       <c r="H86" t="str">
-        <v>屋島</v>
+        <v>古高松</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B87" t="str">
-        <v>34.32964</v>
+        <v>34.33583333</v>
       </c>
       <c r="C87" t="str">
-        <v>134.087006</v>
+        <v>134.0937228</v>
       </c>
       <c r="D87" t="str">
-        <v>高松大学・高松短期大学</v>
+        <v>ＳＴＮｅｔビル</v>
       </c>
       <c r="E87" t="str">
-        <v>高松市春日町960</v>
+        <v>高松市春日町1735-3</v>
       </c>
       <c r="F87" t="str">
-        <v>本館の２，３，４，５階 ・ 1号館２，３，４階 ・ ２号館の２，３階 ・ 図書館の３階 ・ 学生会館の２階 ・ クラブハウスの２階 ・ 体育館の２階</v>
+        <v>２階・７階</v>
       </c>
       <c r="G87" t="str">
-        <v>2750</v>
+        <v>150</v>
       </c>
       <c r="H87" t="str">
         <v>古高松</v>
@@ -2663,25 +2663,25 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B88" t="str">
-        <v>34.33583333</v>
+        <v>34.33263944</v>
       </c>
       <c r="C88" t="str">
-        <v>134.0937228</v>
+        <v>134.1030886</v>
       </c>
       <c r="D88" t="str">
-        <v>ＳＴＮｅｔビル</v>
+        <v>古高松中学校</v>
       </c>
       <c r="E88" t="str">
-        <v>高松市春日町1735-3</v>
+        <v>高松市新田町甲190-1</v>
       </c>
       <c r="F88" t="str">
-        <v>２階・７階</v>
+        <v>校舎</v>
       </c>
       <c r="G88" t="str">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H88" t="str">
         <v>古高松</v>
@@ -2689,25 +2689,25 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B89" t="str">
-        <v>34.33263944</v>
+        <v>34.32479889</v>
       </c>
       <c r="C89" t="str">
-        <v>134.1030886</v>
+        <v>134.1028306</v>
       </c>
       <c r="D89" t="str">
-        <v>古高松中学校</v>
+        <v>古高松南小学校</v>
       </c>
       <c r="E89" t="str">
-        <v>高松市新田町甲190-1</v>
+        <v>高松市新田町甲2605</v>
       </c>
       <c r="F89" t="str">
         <v>校舎</v>
       </c>
       <c r="G89" t="str">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H89" t="str">
         <v>古高松</v>
@@ -2715,25 +2715,25 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B90" t="str">
-        <v>34.32479889</v>
+        <v>34.32871222</v>
       </c>
       <c r="C90" t="str">
-        <v>134.1028306</v>
+        <v>134.0992336</v>
       </c>
       <c r="D90" t="str">
-        <v>古高松南小学校</v>
+        <v>障害者支援施設サン未来</v>
       </c>
       <c r="E90" t="str">
-        <v>高松市新田町甲2605</v>
+        <v>高松市新田町甲2717-1</v>
       </c>
       <c r="F90" t="str">
-        <v>校舎</v>
+        <v>５階</v>
       </c>
       <c r="G90" t="str">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="H90" t="str">
         <v>古高松</v>
@@ -2741,25 +2741,25 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B91" t="str">
-        <v>34.32871222</v>
+        <v>34.32956806</v>
       </c>
       <c r="C91" t="str">
-        <v>134.0992336</v>
+        <v>134.1187678</v>
       </c>
       <c r="D91" t="str">
-        <v>障害者支援施設サン未来</v>
+        <v>古高松小学校</v>
       </c>
       <c r="E91" t="str">
-        <v>高松市新田町甲2717-1</v>
+        <v>高松市高松町398</v>
       </c>
       <c r="F91" t="str">
-        <v>５階</v>
+        <v>校舎</v>
       </c>
       <c r="G91" t="str">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="H91" t="str">
         <v>古高松</v>
@@ -2767,25 +2767,25 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B92" t="str">
-        <v>34.32956806</v>
+        <v>34.3292175</v>
       </c>
       <c r="C92" t="str">
-        <v>134.1187678</v>
+        <v>134.0992836</v>
       </c>
       <c r="D92" t="str">
-        <v>古高松小学校</v>
+        <v>介護老人保健施設サンライズ屋島</v>
       </c>
       <c r="E92" t="str">
-        <v>高松市高松町398</v>
+        <v>高松市新田町甲2723-2</v>
       </c>
       <c r="F92" t="str">
-        <v>校舎</v>
+        <v>３，４階オープンスペースおよび屋上</v>
       </c>
       <c r="G92" t="str">
-        <v>150</v>
+        <v>850</v>
       </c>
       <c r="H92" t="str">
         <v>古高松</v>
@@ -2793,25 +2793,25 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B93" t="str">
-        <v>34.3292175</v>
+        <v>34.32697333</v>
       </c>
       <c r="C93" t="str">
-        <v>134.0992836</v>
+        <v>134.0917119</v>
       </c>
       <c r="D93" t="str">
-        <v>介護老人保健施設サンライズ屋島</v>
+        <v>古高松南コミュニティセンター</v>
       </c>
       <c r="E93" t="str">
-        <v>高松市新田町甲2723-2</v>
+        <v>高松市春日町782-2</v>
       </c>
       <c r="F93" t="str">
-        <v>３，４階オープンスペースおよび屋上</v>
+        <v>２階</v>
       </c>
       <c r="G93" t="str">
-        <v>850</v>
+        <v>100</v>
       </c>
       <c r="H93" t="str">
         <v>古高松</v>
@@ -2819,25 +2819,25 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B94" t="str">
-        <v>34.32697333</v>
+        <v>34.32746</v>
       </c>
       <c r="C94" t="str">
-        <v>134.0917119</v>
+        <v>134.09237</v>
       </c>
       <c r="D94" t="str">
-        <v>古高松南コミュニティセンター</v>
+        <v>トヨタカローラ香川株式会社春日店</v>
       </c>
       <c r="E94" t="str">
-        <v>高松市春日町782-2</v>
+        <v>高松市春日町902-1</v>
       </c>
       <c r="F94" t="str">
-        <v>２階</v>
+        <v>店舗２階イベントホール</v>
       </c>
       <c r="G94" t="str">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="H94" t="str">
         <v>古高松</v>
@@ -2845,77 +2845,77 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B95" t="str">
-        <v>34.32746</v>
+        <v>34.34978</v>
       </c>
       <c r="C95" t="str">
-        <v>134.09237</v>
+        <v>134.00953</v>
       </c>
       <c r="D95" t="str">
-        <v>トヨタカローラ香川株式会社春日店</v>
+        <v>フソウテクノセンター</v>
       </c>
       <c r="E95" t="str">
-        <v>高松市春日町902-1</v>
+        <v>高松市郷東町792-8</v>
       </c>
       <c r="F95" t="str">
-        <v>店舗２階イベントホール</v>
+        <v>2階 体育館ホール、ギャラリー、トレーニングスペース</v>
       </c>
       <c r="G95" t="str">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="H95" t="str">
-        <v>古高松</v>
+        <v>弦打</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B96" t="str">
-        <v>34.34978</v>
+        <v>34.35095472</v>
       </c>
       <c r="C96" t="str">
-        <v>134.00953</v>
+        <v>134.0031525</v>
       </c>
       <c r="D96" t="str">
-        <v>フソウテクノセンター</v>
+        <v>イオン高松店</v>
       </c>
       <c r="E96" t="str">
-        <v>高松市郷東町792-8</v>
+        <v>高松市香西本町1-1</v>
       </c>
       <c r="F96" t="str">
-        <v>2階 体育館ホール、ギャラリー、トレーニングスペース</v>
+        <v>４階と屋上の駐車場部分</v>
       </c>
       <c r="G96" t="str">
-        <v>113</v>
+        <v>10000</v>
       </c>
       <c r="H96" t="str">
-        <v>弦打</v>
+        <v>香西</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B97" t="str">
-        <v>34.35095472</v>
+        <v>34.34682444</v>
       </c>
       <c r="C97" t="str">
-        <v>134.0031525</v>
+        <v>133.99622</v>
       </c>
       <c r="D97" t="str">
-        <v>イオン高松店</v>
+        <v>香西コミュニティセンター</v>
       </c>
       <c r="E97" t="str">
-        <v>高松市香西本町1-1</v>
+        <v>高松市香西本町476-1</v>
       </c>
       <c r="F97" t="str">
-        <v>４階と屋上の駐車場部分</v>
+        <v>２階</v>
       </c>
       <c r="G97" t="str">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="H97" t="str">
         <v>香西</v>
@@ -2923,25 +2923,25 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B98" t="str">
-        <v>34.34682444</v>
+        <v>34.34290278</v>
       </c>
       <c r="C98" t="str">
-        <v>133.99622</v>
+        <v>134.0037278</v>
       </c>
       <c r="D98" t="str">
-        <v>香西コミュニティセンター</v>
+        <v>パーラーグランド香西</v>
       </c>
       <c r="E98" t="str">
-        <v>高松市香西本町476-1</v>
+        <v>高松市香西南町378-1</v>
       </c>
       <c r="F98" t="str">
-        <v>２階</v>
+        <v>立体駐車場の２階から屋上まで</v>
       </c>
       <c r="G98" t="str">
-        <v>100</v>
+        <v>3600</v>
       </c>
       <c r="H98" t="str">
         <v>香西</v>
@@ -2949,25 +2949,25 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B99" t="str">
-        <v>34.34290278</v>
+        <v>34.34211111</v>
       </c>
       <c r="C99" t="str">
-        <v>134.0037278</v>
+        <v>134.0007281</v>
       </c>
       <c r="D99" t="str">
-        <v>パーラーグランド香西</v>
+        <v>ふれあい福祉センター勝賀</v>
       </c>
       <c r="E99" t="str">
-        <v>高松市香西南町378-1</v>
+        <v>高松市香西南町476-1</v>
       </c>
       <c r="F99" t="str">
-        <v>立体駐車場の２階から屋上まで</v>
+        <v>２階</v>
       </c>
       <c r="G99" t="str">
-        <v>3600</v>
+        <v>100</v>
       </c>
       <c r="H99" t="str">
         <v>香西</v>
@@ -2975,22 +2975,22 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B100" t="str">
-        <v>34.34211111</v>
+        <v>34.33905028</v>
       </c>
       <c r="C100" t="str">
-        <v>134.0007281</v>
+        <v>133.9978061</v>
       </c>
       <c r="D100" t="str">
-        <v>ふれあい福祉センター勝賀</v>
+        <v>勝賀中学校</v>
       </c>
       <c r="E100" t="str">
-        <v>高松市香西南町476-1</v>
+        <v>高松市香西南町565</v>
       </c>
       <c r="F100" t="str">
-        <v>２階</v>
+        <v>校舎</v>
       </c>
       <c r="G100" t="str">
         <v>100</v>
@@ -3001,25 +3001,25 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B101" t="str">
-        <v>34.33905028</v>
+        <v>34.34546083</v>
       </c>
       <c r="C101" t="str">
-        <v>133.9978061</v>
+        <v>133.9979003</v>
       </c>
       <c r="D101" t="str">
-        <v>勝賀中学校</v>
+        <v>香西小学校</v>
       </c>
       <c r="E101" t="str">
-        <v>高松市香西南町565</v>
+        <v>高松市香西南町703-1</v>
       </c>
       <c r="F101" t="str">
         <v>校舎</v>
       </c>
       <c r="G101" t="str">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H101" t="str">
         <v>香西</v>
@@ -3027,25 +3027,25 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B102" t="str">
-        <v>34.34546083</v>
+        <v>34.35634</v>
       </c>
       <c r="C102" t="str">
-        <v>133.9979003</v>
+        <v>133.9888564</v>
       </c>
       <c r="D102" t="str">
-        <v>香西小学校</v>
+        <v>特別養護老人ホームシオンの丘ホーム</v>
       </c>
       <c r="E102" t="str">
-        <v>高松市香西南町703-1</v>
+        <v>高松市香西北町260</v>
       </c>
       <c r="F102" t="str">
-        <v>校舎</v>
+        <v>４階テラス部分と屋上</v>
       </c>
       <c r="G102" t="str">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H102" t="str">
         <v>香西</v>
@@ -3053,25 +3053,25 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B103" t="str">
-        <v>34.35634</v>
+        <v>34.34254472</v>
       </c>
       <c r="C103" t="str">
-        <v>133.9888564</v>
+        <v>134.007305</v>
       </c>
       <c r="D103" t="str">
-        <v>特別養護老人ホームシオンの丘ホーム</v>
+        <v>ＤＣＭダイキ香西店</v>
       </c>
       <c r="E103" t="str">
-        <v>高松市香西北町260</v>
+        <v>高松市香西東町350-1</v>
       </c>
       <c r="F103" t="str">
-        <v>４階テラス部分と屋上</v>
+        <v>屋上駐車場</v>
       </c>
       <c r="G103" t="str">
-        <v>250</v>
+        <v>800</v>
       </c>
       <c r="H103" t="str">
         <v>香西</v>
@@ -3079,51 +3079,51 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B104" t="str">
-        <v>34.34254472</v>
+        <v>34.35712528</v>
       </c>
       <c r="C104" t="str">
-        <v>134.007305</v>
+        <v>133.9559758</v>
       </c>
       <c r="D104" t="str">
-        <v>ＤＣＭダイキ香西店</v>
+        <v>下笠居小学校</v>
       </c>
       <c r="E104" t="str">
-        <v>高松市香西東町350-1</v>
+        <v>高松市生島町345</v>
       </c>
       <c r="F104" t="str">
-        <v>屋上駐車場</v>
+        <v>体育館</v>
       </c>
       <c r="G104" t="str">
-        <v>800</v>
+        <v>550</v>
       </c>
       <c r="H104" t="str">
-        <v>香西</v>
+        <v>下笠居</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B105" t="str">
-        <v>34.35712528</v>
+        <v>34.35870861</v>
       </c>
       <c r="C105" t="str">
-        <v>133.9559758</v>
+        <v>133.9687664</v>
       </c>
       <c r="D105" t="str">
-        <v>下笠居小学校</v>
+        <v>下笠居コミュニティセンター</v>
       </c>
       <c r="E105" t="str">
-        <v>高松市生島町345</v>
+        <v>高松市生島町353-1</v>
       </c>
       <c r="F105" t="str">
-        <v>体育館</v>
+        <v>施設内</v>
       </c>
       <c r="G105" t="str">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="H105" t="str">
         <v>下笠居</v>
@@ -3131,25 +3131,25 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B106" t="str">
-        <v>34.35870861</v>
+        <v>34.35771139</v>
       </c>
       <c r="C106" t="str">
-        <v>133.9687664</v>
+        <v>133.9666417</v>
       </c>
       <c r="D106" t="str">
-        <v>下笠居コミュニティセンター</v>
+        <v>下笠居中学校</v>
       </c>
       <c r="E106" t="str">
-        <v>高松市生島町353-1</v>
+        <v>高松市生島町372-1</v>
       </c>
       <c r="F106" t="str">
-        <v>施設内</v>
+        <v>体育館</v>
       </c>
       <c r="G106" t="str">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="H106" t="str">
         <v>下笠居</v>
@@ -3157,51 +3157,51 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B107" t="str">
-        <v>34.35771139</v>
+        <v>34.33324056</v>
       </c>
       <c r="C107" t="str">
-        <v>133.9666417</v>
+        <v>134.1535814</v>
       </c>
       <c r="D107" t="str">
-        <v>下笠居中学校</v>
+        <v>牟礼南小学校</v>
       </c>
       <c r="E107" t="str">
-        <v>高松市生島町372-1</v>
+        <v>高松市牟礼町大町1115-1</v>
       </c>
       <c r="F107" t="str">
-        <v>体育館</v>
+        <v>校舎</v>
       </c>
       <c r="G107" t="str">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="H107" t="str">
-        <v>下笠居</v>
+        <v>牟礼</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B108" t="str">
-        <v>34.33324056</v>
+        <v>34.33351</v>
       </c>
       <c r="C108" t="str">
-        <v>134.1535814</v>
+        <v>134.1567117</v>
       </c>
       <c r="D108" t="str">
-        <v>牟礼南小学校</v>
+        <v>道の駅源平の里むれ</v>
       </c>
       <c r="E108" t="str">
-        <v>高松市牟礼町大町1115-1</v>
+        <v>高松市牟礼町原631-7</v>
       </c>
       <c r="F108" t="str">
-        <v>校舎</v>
+        <v>物産館および真念堂</v>
       </c>
       <c r="G108" t="str">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H108" t="str">
         <v>牟礼</v>
@@ -3209,45 +3209,45 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B109" t="str">
-        <v>34.33351</v>
+        <v>34.38324278</v>
       </c>
       <c r="C109" t="str">
-        <v>134.1567117</v>
+        <v>134.1307706</v>
       </c>
       <c r="D109" t="str">
-        <v>道の駅源平の里むれ</v>
+        <v>庵治中学校</v>
       </c>
       <c r="E109" t="str">
-        <v>高松市牟礼町原631-7</v>
+        <v>高松市庵治町691-1</v>
       </c>
       <c r="F109" t="str">
-        <v>物産館および真念堂</v>
+        <v>校舎</v>
       </c>
       <c r="G109" t="str">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H109" t="str">
-        <v>牟礼</v>
+        <v>庵治</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B110" t="str">
-        <v>34.38324278</v>
+        <v>34.3844425</v>
       </c>
       <c r="C110" t="str">
-        <v>134.1307706</v>
+        <v>134.1318539</v>
       </c>
       <c r="D110" t="str">
-        <v>庵治中学校</v>
+        <v>庵治小学校</v>
       </c>
       <c r="E110" t="str">
-        <v>高松市庵治町691-1</v>
+        <v>高松市庵治町790-1</v>
       </c>
       <c r="F110" t="str">
         <v>校舎</v>
@@ -3261,25 +3261,25 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B111" t="str">
-        <v>34.3844425</v>
+        <v>34.3853175</v>
       </c>
       <c r="C111" t="str">
-        <v>134.1318539</v>
+        <v>134.1299483</v>
       </c>
       <c r="D111" t="str">
-        <v>庵治小学校</v>
+        <v>庵治コミュニティセンター</v>
       </c>
       <c r="E111" t="str">
-        <v>高松市庵治町790-1</v>
+        <v>高松市庵治町888-1</v>
       </c>
       <c r="F111" t="str">
-        <v>校舎</v>
+        <v>２階</v>
       </c>
       <c r="G111" t="str">
-        <v>100</v>
+        <v>850</v>
       </c>
       <c r="H111" t="str">
         <v>庵治</v>
@@ -3287,25 +3287,25 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B112" t="str">
-        <v>34.3853175</v>
+        <v>34.38328139</v>
       </c>
       <c r="C112" t="str">
-        <v>134.1299483</v>
+        <v>134.1249322</v>
       </c>
       <c r="D112" t="str">
-        <v>庵治コミュニティセンター</v>
+        <v>庵治やすらぎ会館</v>
       </c>
       <c r="E112" t="str">
-        <v>高松市庵治町888-1</v>
+        <v>高松市庵治町6392-14</v>
       </c>
       <c r="F112" t="str">
         <v>２階</v>
       </c>
       <c r="G112" t="str">
-        <v>850</v>
+        <v>50</v>
       </c>
       <c r="H112" t="str">
         <v>庵治</v>
@@ -3313,22 +3313,22 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B113" t="str">
-        <v>34.38328139</v>
+        <v>34.38463139</v>
       </c>
       <c r="C113" t="str">
-        <v>134.1249322</v>
+        <v>134.1264239</v>
       </c>
       <c r="D113" t="str">
-        <v>庵治やすらぎ会館</v>
+        <v>庵治支所</v>
       </c>
       <c r="E113" t="str">
-        <v>高松市庵治町6392-14</v>
+        <v>高松市庵治町6393-5</v>
       </c>
       <c r="F113" t="str">
-        <v>２階</v>
+        <v>議会棟</v>
       </c>
       <c r="G113" t="str">
         <v>50</v>
@@ -3339,59 +3339,33 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B114" t="str">
-        <v>34.38463139</v>
+        <v>34.388357</v>
       </c>
       <c r="C114" t="str">
-        <v>134.1264239</v>
+        <v>134.129479</v>
       </c>
       <c r="D114" t="str">
-        <v>庵治支所</v>
+        <v>庵治保健センター（ほっとぴあん）</v>
       </c>
       <c r="E114" t="str">
-        <v>高松市庵治町6393-5</v>
+        <v>高松市庵治町978</v>
       </c>
       <c r="F114" t="str">
-        <v>議会棟</v>
+        <v>バルコニー部分</v>
       </c>
       <c r="G114" t="str">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="H114" t="str">
         <v>庵治</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="str">
-        <v>114</v>
-      </c>
-      <c r="B115" t="str">
-        <v>34.388357</v>
-      </c>
-      <c r="C115" t="str">
-        <v>134.129479</v>
-      </c>
-      <c r="D115" t="str">
-        <v>庵治保健センター（ほっとぴあん）</v>
-      </c>
-      <c r="E115" t="str">
-        <v>高松市庵治町978</v>
-      </c>
-      <c r="F115" t="str">
-        <v>バルコニー部分</v>
-      </c>
-      <c r="G115" t="str">
-        <v>200</v>
-      </c>
-      <c r="H115" t="str">
-        <v>庵治</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H115"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H114"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tsunami_evacuation_building/data.xlsx
+++ b/data/tsunami_evacuation_building/data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:H113"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1753,7 +1753,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B53" t="str">
         <v>34.352575</v>
@@ -1762,16 +1762,16 @@
         <v>134.0470042</v>
       </c>
       <c r="D53" t="str">
-        <v>高松シンボルタワー　かがわプラザ</v>
+        <v>高松シンボルタワー　共用部</v>
       </c>
       <c r="E53" t="str">
         <v>高松市サンポート2-1</v>
       </c>
       <c r="F53" t="str">
-        <v>インフォメーションゾーン</v>
+        <v>３階・４階・７階・８階の一部</v>
       </c>
       <c r="G53" t="str">
-        <v>250</v>
+        <v>1500</v>
       </c>
       <c r="H53" t="str">
         <v>二番丁</v>
@@ -1779,51 +1779,51 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B54" t="str">
-        <v>34.352575</v>
+        <v>34.3471725</v>
       </c>
       <c r="C54" t="str">
-        <v>134.0470042</v>
+        <v>134.0301975</v>
       </c>
       <c r="D54" t="str">
-        <v>高松シンボルタワー　共用部</v>
+        <v>日新小学校跡施設</v>
       </c>
       <c r="E54" t="str">
-        <v>高松市サンポート2-1</v>
+        <v>高松市瀬戸内町18-2</v>
       </c>
       <c r="F54" t="str">
-        <v>３階・４階・７階・８階の一部</v>
+        <v>体育館</v>
       </c>
       <c r="G54" t="str">
-        <v>1500</v>
+        <v>400</v>
       </c>
       <c r="H54" t="str">
-        <v>二番丁</v>
+        <v>日新</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B55" t="str">
-        <v>34.3471725</v>
+        <v>34.34767528</v>
       </c>
       <c r="C55" t="str">
-        <v>134.0301975</v>
+        <v>134.0326083</v>
       </c>
       <c r="D55" t="str">
-        <v>日新小学校跡施設</v>
+        <v>日新コミュニティセンター</v>
       </c>
       <c r="E55" t="str">
-        <v>高松市瀬戸内町18-2</v>
+        <v>高松市瀬戸内町22-9</v>
       </c>
       <c r="F55" t="str">
-        <v>体育館</v>
+        <v>２階</v>
       </c>
       <c r="G55" t="str">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H55" t="str">
         <v>日新</v>
@@ -1831,51 +1831,51 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B56" t="str">
-        <v>34.34767528</v>
+        <v>34.33778472</v>
       </c>
       <c r="C56" t="str">
-        <v>134.0326083</v>
+        <v>134.0400219</v>
       </c>
       <c r="D56" t="str">
-        <v>日新コミュニティセンター</v>
+        <v>亀阜小学校</v>
       </c>
       <c r="E56" t="str">
-        <v>高松市瀬戸内町22-9</v>
+        <v>高松市亀岡町10-1</v>
       </c>
       <c r="F56" t="str">
-        <v>２階</v>
+        <v>校舎</v>
       </c>
       <c r="G56" t="str">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H56" t="str">
-        <v>日新</v>
+        <v>亀阜</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B57" t="str">
-        <v>34.33778472</v>
+        <v>34.33931222</v>
       </c>
       <c r="C57" t="str">
-        <v>134.0400219</v>
+        <v>134.0354667</v>
       </c>
       <c r="D57" t="str">
-        <v>亀阜小学校</v>
+        <v>亀阜コミュニティセンター</v>
       </c>
       <c r="E57" t="str">
-        <v>高松市亀岡町10-1</v>
+        <v>高松市宮脇町一丁目6-18</v>
       </c>
       <c r="F57" t="str">
-        <v>校舎</v>
+        <v>２階</v>
       </c>
       <c r="G57" t="str">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="H57" t="str">
         <v>亀阜</v>
@@ -1883,25 +1883,25 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B58" t="str">
-        <v>34.33931222</v>
+        <v>34.34047583</v>
       </c>
       <c r="C58" t="str">
-        <v>134.0354667</v>
+        <v>134.0301781</v>
       </c>
       <c r="D58" t="str">
-        <v>亀阜コミュニティセンター</v>
+        <v>香川県教育会館（ミューズホール）</v>
       </c>
       <c r="E58" t="str">
-        <v>高松市宮脇町一丁目6-18</v>
+        <v>高松市西宝町二丁目6-40</v>
       </c>
       <c r="F58" t="str">
-        <v>２階</v>
+        <v>２階・３階・５階・６階の会議室</v>
       </c>
       <c r="G58" t="str">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="H58" t="str">
         <v>亀阜</v>
@@ -1909,22 +1909,22 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B59" t="str">
-        <v>34.34047583</v>
+        <v>34.342945</v>
       </c>
       <c r="C59" t="str">
-        <v>134.0301781</v>
+        <v>134.0261256</v>
       </c>
       <c r="D59" t="str">
-        <v>香川県教育会館（ミューズホール）</v>
+        <v>喜代美山荘　花樹海</v>
       </c>
       <c r="E59" t="str">
-        <v>高松市西宝町二丁目6-40</v>
+        <v>高松市西宝町三丁目5-10</v>
       </c>
       <c r="F59" t="str">
-        <v>２階・３階・５階・６階の会議室</v>
+        <v>１階ロビー</v>
       </c>
       <c r="G59" t="str">
         <v>400</v>
@@ -1935,25 +1935,25 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B60" t="str">
-        <v>34.342945</v>
+        <v>34.34042333</v>
       </c>
       <c r="C60" t="str">
-        <v>134.0261256</v>
+        <v>134.0337861</v>
       </c>
       <c r="D60" t="str">
-        <v>喜代美山荘　花樹海</v>
+        <v>紫雲中学校</v>
       </c>
       <c r="E60" t="str">
-        <v>高松市西宝町三丁目5-10</v>
+        <v>高松市紫雲町8-25</v>
       </c>
       <c r="F60" t="str">
-        <v>１階ロビー</v>
+        <v>校舎</v>
       </c>
       <c r="G60" t="str">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="H60" t="str">
         <v>亀阜</v>
@@ -1961,25 +1961,25 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B61" t="str">
-        <v>34.34042333</v>
+        <v>34.343799</v>
       </c>
       <c r="C61" t="str">
-        <v>134.0337861</v>
+        <v>134.02003</v>
       </c>
       <c r="D61" t="str">
-        <v>紫雲中学校</v>
+        <v>アナザースタイル</v>
       </c>
       <c r="E61" t="str">
-        <v>高松市紫雲町8-25</v>
+        <v>高松市西宝町3丁目670番地</v>
       </c>
       <c r="F61" t="str">
-        <v>校舎</v>
+        <v>1階</v>
       </c>
       <c r="G61" t="str">
-        <v>1000</v>
+        <v>119</v>
       </c>
       <c r="H61" t="str">
         <v>亀阜</v>
@@ -1987,48 +1987,48 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B62" t="str">
-        <v>34.343799</v>
+        <v>34.319237</v>
       </c>
       <c r="C62" t="str">
-        <v>134.02003</v>
+        <v>134.076215</v>
       </c>
       <c r="D62" t="str">
-        <v>アナザースタイル</v>
+        <v>木太南コミュニティセンター</v>
       </c>
       <c r="E62" t="str">
-        <v>高松市西宝町3丁目670番地</v>
+        <v>高松市木太町1486</v>
       </c>
       <c r="F62" t="str">
-        <v>1階</v>
+        <v>２階</v>
       </c>
       <c r="G62" t="str">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="H62" t="str">
-        <v>亀阜</v>
+        <v>木太</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B63" t="str">
-        <v>34.319237</v>
+        <v>34.32080417</v>
       </c>
       <c r="C63" t="str">
-        <v>134.076215</v>
+        <v>134.0747194</v>
       </c>
       <c r="D63" t="str">
-        <v>木太南コミュニティセンター</v>
+        <v>木太南小学校</v>
       </c>
       <c r="E63" t="str">
-        <v>高松市木太町1486</v>
+        <v>高松市木太町1530-1</v>
       </c>
       <c r="F63" t="str">
-        <v>２階</v>
+        <v>校舎</v>
       </c>
       <c r="G63" t="str">
         <v>50</v>
@@ -2039,25 +2039,25 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B64" t="str">
-        <v>34.32080417</v>
+        <v>34.32491472</v>
       </c>
       <c r="C64" t="str">
-        <v>134.0747194</v>
+        <v>134.0698392</v>
       </c>
       <c r="D64" t="str">
-        <v>木太南小学校</v>
+        <v>香川県農業協同組合木太支店</v>
       </c>
       <c r="E64" t="str">
-        <v>高松市木太町1530-1</v>
+        <v>高松市木太町1669</v>
       </c>
       <c r="F64" t="str">
-        <v>校舎</v>
+        <v>２階</v>
       </c>
       <c r="G64" t="str">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="H64" t="str">
         <v>木太</v>
@@ -2065,25 +2065,25 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B65" t="str">
-        <v>34.32491472</v>
+        <v>34.3336525</v>
       </c>
       <c r="C65" t="str">
-        <v>134.0698392</v>
+        <v>134.0709525</v>
       </c>
       <c r="D65" t="str">
-        <v>香川県農業協同組合木太支店</v>
+        <v>高松国際ホテル</v>
       </c>
       <c r="E65" t="str">
-        <v>高松市木太町1669</v>
+        <v>高松市木太町2191-1</v>
       </c>
       <c r="F65" t="str">
-        <v>２階</v>
+        <v>宴会棟の３階</v>
       </c>
       <c r="G65" t="str">
-        <v>300</v>
+        <v>1050</v>
       </c>
       <c r="H65" t="str">
         <v>木太</v>
@@ -2091,25 +2091,25 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B66" t="str">
-        <v>34.3336525</v>
+        <v>34.3389075</v>
       </c>
       <c r="C66" t="str">
-        <v>134.0709525</v>
+        <v>134.0721661</v>
       </c>
       <c r="D66" t="str">
-        <v>高松国際ホテル</v>
+        <v>環境業務センター</v>
       </c>
       <c r="E66" t="str">
-        <v>高松市木太町2191-1</v>
+        <v>高松市木太町2282-1</v>
       </c>
       <c r="F66" t="str">
-        <v>宴会棟の３階</v>
+        <v>４階</v>
       </c>
       <c r="G66" t="str">
-        <v>1050</v>
+        <v>450</v>
       </c>
       <c r="H66" t="str">
         <v>木太</v>
@@ -2117,25 +2117,25 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B67" t="str">
-        <v>34.3389075</v>
+        <v>34.32491472</v>
       </c>
       <c r="C67" t="str">
-        <v>134.0721661</v>
+        <v>134.0698392</v>
       </c>
       <c r="D67" t="str">
-        <v>環境業務センター</v>
+        <v>マルハン高松店</v>
       </c>
       <c r="E67" t="str">
-        <v>高松市木太町2282-1</v>
+        <v>高松市木太町2425</v>
       </c>
       <c r="F67" t="str">
-        <v>４階</v>
+        <v>立体駐車場の２階以上</v>
       </c>
       <c r="G67" t="str">
-        <v>450</v>
+        <v>6350</v>
       </c>
       <c r="H67" t="str">
         <v>木太</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B68" t="str">
         <v>34.32491472</v>
@@ -2152,16 +2152,16 @@
         <v>134.0698392</v>
       </c>
       <c r="D68" t="str">
-        <v>マルハン高松店</v>
+        <v>木太北部コミュニティセンター</v>
       </c>
       <c r="E68" t="str">
-        <v>高松市木太町2425</v>
+        <v>高松市木太町2603</v>
       </c>
       <c r="F68" t="str">
-        <v>立体駐車場の２階以上</v>
+        <v>２階</v>
       </c>
       <c r="G68" t="str">
-        <v>6350</v>
+        <v>50</v>
       </c>
       <c r="H68" t="str">
         <v>木太</v>
@@ -2169,7 +2169,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B69" t="str">
         <v>34.32491472</v>
@@ -2178,16 +2178,16 @@
         <v>134.0698392</v>
       </c>
       <c r="D69" t="str">
-        <v>木太北部コミュニティセンター</v>
+        <v>木太北部小学校</v>
       </c>
       <c r="E69" t="str">
-        <v>高松市木太町2603</v>
+        <v>高松市木太町2613</v>
       </c>
       <c r="F69" t="str">
-        <v>２階</v>
+        <v>校舎</v>
       </c>
       <c r="G69" t="str">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="H69" t="str">
         <v>木太</v>
@@ -2195,7 +2195,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B70" t="str">
         <v>34.32491472</v>
@@ -2204,16 +2204,16 @@
         <v>134.0698392</v>
       </c>
       <c r="D70" t="str">
-        <v>木太北部小学校</v>
+        <v>木太小学校</v>
       </c>
       <c r="E70" t="str">
-        <v>高松市木太町2613</v>
+        <v>高松市木太町3480</v>
       </c>
       <c r="F70" t="str">
         <v>校舎</v>
       </c>
       <c r="G70" t="str">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="H70" t="str">
         <v>木太</v>
@@ -2221,7 +2221,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B71" t="str">
         <v>34.32491472</v>
@@ -2230,13 +2230,13 @@
         <v>134.0698392</v>
       </c>
       <c r="D71" t="str">
-        <v>木太小学校</v>
+        <v>特別養護老人ホーム法寿苑</v>
       </c>
       <c r="E71" t="str">
-        <v>高松市木太町3480</v>
+        <v>高松市木太町3308</v>
       </c>
       <c r="F71" t="str">
-        <v>校舎</v>
+        <v>３階レクリエーションルーム・３階地域交流ルーム</v>
       </c>
       <c r="G71" t="str">
         <v>200</v>
@@ -2247,25 +2247,25 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B72" t="str">
-        <v>34.32491472</v>
+        <v xml:space="preserve">34.329139 </v>
       </c>
       <c r="C72" t="str">
-        <v>134.0698392</v>
+        <v>134.071112</v>
       </c>
       <c r="D72" t="str">
-        <v>特別養護老人ホーム法寿苑</v>
+        <v>四国財務局合同宿舎深田住宅</v>
       </c>
       <c r="E72" t="str">
-        <v>高松市木太町3308</v>
+        <v>高松市木太町1992</v>
       </c>
       <c r="F72" t="str">
-        <v>３階レクリエーションルーム・３階地域交流ルーム</v>
+        <v>３階・４階・５階の廊下</v>
       </c>
       <c r="G72" t="str">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H72" t="str">
         <v>木太</v>
@@ -2273,22 +2273,22 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B73" t="str">
-        <v xml:space="preserve">34.329139 </v>
+        <v>34.326186</v>
       </c>
       <c r="C73" t="str">
-        <v>134.071112</v>
+        <v>134.076753</v>
       </c>
       <c r="D73" t="str">
-        <v>四国財務局合同宿舎深田住宅</v>
+        <v>木太コミュニティセンター</v>
       </c>
       <c r="E73" t="str">
-        <v>高松市木太町1992</v>
+        <v>高松市木太町3480-2</v>
       </c>
       <c r="F73" t="str">
-        <v>３階・４階・５階の廊下</v>
+        <v>2階</v>
       </c>
       <c r="G73" t="str">
         <v>150</v>
@@ -2299,51 +2299,51 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B74" t="str">
-        <v>34.326186</v>
+        <v>34.3537625</v>
       </c>
       <c r="C74" t="str">
-        <v>134.076753</v>
+        <v>134.1159869</v>
       </c>
       <c r="D74" t="str">
-        <v>木太コミュニティセンター</v>
+        <v>屋島東小学校</v>
       </c>
       <c r="E74" t="str">
-        <v>高松市木太町3480-2</v>
+        <v>高松市屋島東町942-1</v>
       </c>
       <c r="F74" t="str">
-        <v>2階</v>
+        <v>体育館</v>
       </c>
       <c r="G74" t="str">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H74" t="str">
-        <v>木太</v>
+        <v>屋島</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B75" t="str">
-        <v>34.3537625</v>
+        <v>34.34742667</v>
       </c>
       <c r="C75" t="str">
-        <v>134.1159869</v>
+        <v>134.1031936</v>
       </c>
       <c r="D75" t="str">
-        <v>屋島東小学校</v>
+        <v>屋島中学校</v>
       </c>
       <c r="E75" t="str">
-        <v>高松市屋島東町942-1</v>
+        <v>高松市屋島中町295</v>
       </c>
       <c r="F75" t="str">
-        <v>体育館</v>
+        <v>校舎</v>
       </c>
       <c r="G75" t="str">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="H75" t="str">
         <v>屋島</v>
@@ -2351,25 +2351,25 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B76" t="str">
-        <v>34.34742667</v>
+        <v>34.347035</v>
       </c>
       <c r="C76" t="str">
-        <v>134.1031936</v>
+        <v>134.0996331</v>
       </c>
       <c r="D76" t="str">
-        <v>屋島中学校</v>
+        <v>屋島小学校</v>
       </c>
       <c r="E76" t="str">
-        <v>高松市屋島中町295</v>
+        <v>高松市屋島西町1205-1</v>
       </c>
       <c r="F76" t="str">
-        <v>校舎</v>
+        <v>体育館</v>
       </c>
       <c r="G76" t="str">
-        <v>100</v>
+        <v>650</v>
       </c>
       <c r="H76" t="str">
         <v>屋島</v>
@@ -2377,25 +2377,25 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B77" t="str">
-        <v>34.347035</v>
+        <v>34.36114722</v>
       </c>
       <c r="C77" t="str">
-        <v>134.0996331</v>
+        <v>134.0943553</v>
       </c>
       <c r="D77" t="str">
-        <v>屋島小学校</v>
+        <v>株式会社マルナカ　パワーシティ屋島</v>
       </c>
       <c r="E77" t="str">
-        <v>高松市屋島西町1205-1</v>
+        <v>高松市屋島西町1907-1</v>
       </c>
       <c r="F77" t="str">
-        <v>体育館</v>
+        <v>立体駐車場の２階・３階</v>
       </c>
       <c r="G77" t="str">
-        <v>650</v>
+        <v>2850</v>
       </c>
       <c r="H77" t="str">
         <v>屋島</v>
@@ -2403,25 +2403,25 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B78" t="str">
-        <v>34.36114722</v>
+        <v>34.34418222</v>
       </c>
       <c r="C78" t="str">
-        <v>134.0943553</v>
+        <v>134.0881619</v>
       </c>
       <c r="D78" t="str">
-        <v>株式会社マルナカ　パワーシティ屋島</v>
+        <v>西村ジョイ屋島店</v>
       </c>
       <c r="E78" t="str">
-        <v>高松市屋島西町1907-1</v>
+        <v>高松市屋島西町2105-8</v>
       </c>
       <c r="F78" t="str">
-        <v>立体駐車場の２階・３階</v>
+        <v>立体駐車場の２階と屋上</v>
       </c>
       <c r="G78" t="str">
-        <v>2850</v>
+        <v>8000</v>
       </c>
       <c r="H78" t="str">
         <v>屋島</v>
@@ -2429,25 +2429,25 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B79" t="str">
-        <v>34.34418222</v>
+        <v>34.35843639</v>
       </c>
       <c r="C79" t="str">
-        <v>134.0881619</v>
+        <v>134.0893058</v>
       </c>
       <c r="D79" t="str">
-        <v>西村ジョイ屋島店</v>
+        <v>社会福祉法人楽生会ケアハウス屋島</v>
       </c>
       <c r="E79" t="str">
-        <v>高松市屋島西町2105-8</v>
+        <v>高松市屋島西町2277-1</v>
       </c>
       <c r="F79" t="str">
-        <v>立体駐車場の２階と屋上</v>
+        <v>５階</v>
       </c>
       <c r="G79" t="str">
-        <v>8000</v>
+        <v>450</v>
       </c>
       <c r="H79" t="str">
         <v>屋島</v>
@@ -2455,25 +2455,25 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B80" t="str">
-        <v>34.35843639</v>
+        <v>34.34645269</v>
       </c>
       <c r="C80" t="str">
-        <v>134.0893058</v>
+        <v>134.0859116</v>
       </c>
       <c r="D80" t="str">
-        <v>社会福祉法人楽生会ケアハウス屋島</v>
+        <v>せとうち観光専門職短期大学</v>
       </c>
       <c r="E80" t="str">
-        <v>高松市屋島西町2277-1</v>
+        <v>高松市屋島西町2366-1</v>
       </c>
       <c r="F80" t="str">
-        <v>５階</v>
+        <v>２階から４階まで</v>
       </c>
       <c r="G80" t="str">
-        <v>450</v>
+        <v>2500</v>
       </c>
       <c r="H80" t="str">
         <v>屋島</v>
@@ -2481,25 +2481,25 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B81" t="str">
-        <v>34.34645269</v>
+        <v>34.36114722</v>
       </c>
       <c r="C81" t="str">
-        <v>134.0859116</v>
+        <v>134.0943553</v>
       </c>
       <c r="D81" t="str">
-        <v>せとうち観光専門職短期大学</v>
+        <v>屋島西小学校</v>
       </c>
       <c r="E81" t="str">
-        <v>高松市屋島西町2366-1</v>
+        <v>高松市屋島西町2469</v>
       </c>
       <c r="F81" t="str">
-        <v>２階から４階まで</v>
+        <v>校舎</v>
       </c>
       <c r="G81" t="str">
-        <v>2500</v>
+        <v>200</v>
       </c>
       <c r="H81" t="str">
         <v>屋島</v>
@@ -2507,25 +2507,25 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B82" t="str">
-        <v>34.36114722</v>
+        <v>34.35227583</v>
       </c>
       <c r="C82" t="str">
-        <v>134.0943553</v>
+        <v>134.0891614</v>
       </c>
       <c r="D82" t="str">
-        <v>屋島西小学校</v>
+        <v>屋島西コミュニティセンター</v>
       </c>
       <c r="E82" t="str">
-        <v>高松市屋島西町2469</v>
+        <v>高松市屋島西町2483-2</v>
       </c>
       <c r="F82" t="str">
-        <v>校舎</v>
+        <v>２階</v>
       </c>
       <c r="G82" t="str">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="H82" t="str">
         <v>屋島</v>
@@ -2533,25 +2533,25 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B83" t="str">
-        <v>34.35227583</v>
+        <v>34.35927806</v>
       </c>
       <c r="C83" t="str">
-        <v>134.0891614</v>
+        <v>134.10301</v>
       </c>
       <c r="D83" t="str">
-        <v>屋島西コミュニティセンター</v>
+        <v>屋島東コミュニティセンター</v>
       </c>
       <c r="E83" t="str">
-        <v>高松市屋島西町2483-2</v>
+        <v>高松市屋島東町928</v>
       </c>
       <c r="F83" t="str">
-        <v>２階</v>
+        <v>１階・２階</v>
       </c>
       <c r="G83" t="str">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H83" t="str">
         <v>屋島</v>
@@ -2559,25 +2559,25 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B84" t="str">
-        <v>34.35927806</v>
+        <v>34.36114722</v>
       </c>
       <c r="C84" t="str">
-        <v>134.10301</v>
+        <v>134.0943553</v>
       </c>
       <c r="D84" t="str">
-        <v>屋島東コミュニティセンター</v>
+        <v>四国財務局合同宿舎屋島住宅　　　　　　　　　１号棟，２号棟</v>
       </c>
       <c r="E84" t="str">
-        <v>高松市屋島東町928</v>
+        <v>高松市屋島西町1403</v>
       </c>
       <c r="F84" t="str">
-        <v>１階・２階</v>
+        <v>３階から６階の廊下部分</v>
       </c>
       <c r="G84" t="str">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="H84" t="str">
         <v>屋島</v>
@@ -2585,51 +2585,51 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B85" t="str">
-        <v>34.36114722</v>
+        <v>34.32964</v>
       </c>
       <c r="C85" t="str">
-        <v>134.0943553</v>
+        <v>134.087006</v>
       </c>
       <c r="D85" t="str">
-        <v>四国財務局合同宿舎屋島住宅　　　　　　　　　１号棟，２号棟</v>
+        <v>高松大学・高松短期大学</v>
       </c>
       <c r="E85" t="str">
-        <v>高松市屋島西町1403</v>
+        <v>高松市春日町960</v>
       </c>
       <c r="F85" t="str">
-        <v>３階から６階の廊下部分</v>
+        <v>本館の２，３，４，５階 ・ 1号館２，３，４階 ・ ２号館の２，３階 ・ 図書館の３階 ・ 学生会館の２階 ・ クラブハウスの２階 ・ 体育館の２階</v>
       </c>
       <c r="G85" t="str">
-        <v>1100</v>
+        <v>2750</v>
       </c>
       <c r="H85" t="str">
-        <v>屋島</v>
+        <v>古高松</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B86" t="str">
-        <v>34.32964</v>
+        <v>34.33583333</v>
       </c>
       <c r="C86" t="str">
-        <v>134.087006</v>
+        <v>134.0937228</v>
       </c>
       <c r="D86" t="str">
-        <v>高松大学・高松短期大学</v>
+        <v>ＳＴＮｅｔビル</v>
       </c>
       <c r="E86" t="str">
-        <v>高松市春日町960</v>
+        <v>高松市春日町1735-3</v>
       </c>
       <c r="F86" t="str">
-        <v>本館の２，３，４，５階 ・ 1号館２，３，４階 ・ ２号館の２，３階 ・ 図書館の３階 ・ 学生会館の２階 ・ クラブハウスの２階 ・ 体育館の２階</v>
+        <v>２階・７階</v>
       </c>
       <c r="G86" t="str">
-        <v>2750</v>
+        <v>150</v>
       </c>
       <c r="H86" t="str">
         <v>古高松</v>
@@ -2637,25 +2637,25 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B87" t="str">
-        <v>34.33583333</v>
+        <v>34.33263944</v>
       </c>
       <c r="C87" t="str">
-        <v>134.0937228</v>
+        <v>134.1030886</v>
       </c>
       <c r="D87" t="str">
-        <v>ＳＴＮｅｔビル</v>
+        <v>古高松中学校</v>
       </c>
       <c r="E87" t="str">
-        <v>高松市春日町1735-3</v>
+        <v>高松市新田町甲190-1</v>
       </c>
       <c r="F87" t="str">
-        <v>２階・７階</v>
+        <v>校舎</v>
       </c>
       <c r="G87" t="str">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H87" t="str">
         <v>古高松</v>
@@ -2663,25 +2663,25 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B88" t="str">
-        <v>34.33263944</v>
+        <v>34.32479889</v>
       </c>
       <c r="C88" t="str">
-        <v>134.1030886</v>
+        <v>134.1028306</v>
       </c>
       <c r="D88" t="str">
-        <v>古高松中学校</v>
+        <v>古高松南小学校</v>
       </c>
       <c r="E88" t="str">
-        <v>高松市新田町甲190-1</v>
+        <v>高松市新田町甲2605</v>
       </c>
       <c r="F88" t="str">
         <v>校舎</v>
       </c>
       <c r="G88" t="str">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="H88" t="str">
         <v>古高松</v>
@@ -2689,25 +2689,25 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B89" t="str">
-        <v>34.32479889</v>
+        <v>34.32871222</v>
       </c>
       <c r="C89" t="str">
-        <v>134.1028306</v>
+        <v>134.0992336</v>
       </c>
       <c r="D89" t="str">
-        <v>古高松南小学校</v>
+        <v>障害者支援施設サン未来</v>
       </c>
       <c r="E89" t="str">
-        <v>高松市新田町甲2605</v>
+        <v>高松市新田町甲2717-1</v>
       </c>
       <c r="F89" t="str">
-        <v>校舎</v>
+        <v>５階</v>
       </c>
       <c r="G89" t="str">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="H89" t="str">
         <v>古高松</v>
@@ -2715,25 +2715,25 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B90" t="str">
-        <v>34.32871222</v>
+        <v>34.32956806</v>
       </c>
       <c r="C90" t="str">
-        <v>134.0992336</v>
+        <v>134.1187678</v>
       </c>
       <c r="D90" t="str">
-        <v>障害者支援施設サン未来</v>
+        <v>古高松小学校</v>
       </c>
       <c r="E90" t="str">
-        <v>高松市新田町甲2717-1</v>
+        <v>高松市高松町398</v>
       </c>
       <c r="F90" t="str">
-        <v>５階</v>
+        <v>校舎</v>
       </c>
       <c r="G90" t="str">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="H90" t="str">
         <v>古高松</v>
@@ -2741,25 +2741,25 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B91" t="str">
-        <v>34.32956806</v>
+        <v>34.3292175</v>
       </c>
       <c r="C91" t="str">
-        <v>134.1187678</v>
+        <v>134.0992836</v>
       </c>
       <c r="D91" t="str">
-        <v>古高松小学校</v>
+        <v>介護老人保健施設サンライズ屋島</v>
       </c>
       <c r="E91" t="str">
-        <v>高松市高松町398</v>
+        <v>高松市新田町甲2723-2</v>
       </c>
       <c r="F91" t="str">
-        <v>校舎</v>
+        <v>３，４階オープンスペースおよび屋上</v>
       </c>
       <c r="G91" t="str">
-        <v>150</v>
+        <v>850</v>
       </c>
       <c r="H91" t="str">
         <v>古高松</v>
@@ -2767,25 +2767,25 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B92" t="str">
-        <v>34.3292175</v>
+        <v>34.32697333</v>
       </c>
       <c r="C92" t="str">
-        <v>134.0992836</v>
+        <v>134.0917119</v>
       </c>
       <c r="D92" t="str">
-        <v>介護老人保健施設サンライズ屋島</v>
+        <v>古高松南コミュニティセンター</v>
       </c>
       <c r="E92" t="str">
-        <v>高松市新田町甲2723-2</v>
+        <v>高松市春日町782-2</v>
       </c>
       <c r="F92" t="str">
-        <v>３，４階オープンスペースおよび屋上</v>
+        <v>２階</v>
       </c>
       <c r="G92" t="str">
-        <v>850</v>
+        <v>100</v>
       </c>
       <c r="H92" t="str">
         <v>古高松</v>
@@ -2793,25 +2793,25 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B93" t="str">
-        <v>34.32697333</v>
+        <v>34.32746</v>
       </c>
       <c r="C93" t="str">
-        <v>134.0917119</v>
+        <v>134.09237</v>
       </c>
       <c r="D93" t="str">
-        <v>古高松南コミュニティセンター</v>
+        <v>トヨタカローラ香川株式会社春日店</v>
       </c>
       <c r="E93" t="str">
-        <v>高松市春日町782-2</v>
+        <v>高松市春日町902-1</v>
       </c>
       <c r="F93" t="str">
-        <v>２階</v>
+        <v>店舗２階イベントホール</v>
       </c>
       <c r="G93" t="str">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="H93" t="str">
         <v>古高松</v>
@@ -2819,77 +2819,77 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B94" t="str">
-        <v>34.32746</v>
+        <v>34.34978</v>
       </c>
       <c r="C94" t="str">
-        <v>134.09237</v>
+        <v>134.00953</v>
       </c>
       <c r="D94" t="str">
-        <v>トヨタカローラ香川株式会社春日店</v>
+        <v>フソウテクノセンター</v>
       </c>
       <c r="E94" t="str">
-        <v>高松市春日町902-1</v>
+        <v>高松市郷東町792-8</v>
       </c>
       <c r="F94" t="str">
-        <v>店舗２階イベントホール</v>
+        <v>2階 体育館ホール、ギャラリー、トレーニングスペース</v>
       </c>
       <c r="G94" t="str">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="H94" t="str">
-        <v>古高松</v>
+        <v>弦打</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B95" t="str">
-        <v>34.34978</v>
+        <v>34.35095472</v>
       </c>
       <c r="C95" t="str">
-        <v>134.00953</v>
+        <v>134.0031525</v>
       </c>
       <c r="D95" t="str">
-        <v>フソウテクノセンター</v>
+        <v>イオン高松店</v>
       </c>
       <c r="E95" t="str">
-        <v>高松市郷東町792-8</v>
+        <v>高松市香西本町1-1</v>
       </c>
       <c r="F95" t="str">
-        <v>2階 体育館ホール、ギャラリー、トレーニングスペース</v>
+        <v>４階と屋上の駐車場部分</v>
       </c>
       <c r="G95" t="str">
-        <v>113</v>
+        <v>10000</v>
       </c>
       <c r="H95" t="str">
-        <v>弦打</v>
+        <v>香西</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B96" t="str">
-        <v>34.35095472</v>
+        <v>34.34682444</v>
       </c>
       <c r="C96" t="str">
-        <v>134.0031525</v>
+        <v>133.99622</v>
       </c>
       <c r="D96" t="str">
-        <v>イオン高松店</v>
+        <v>香西コミュニティセンター</v>
       </c>
       <c r="E96" t="str">
-        <v>高松市香西本町1-1</v>
+        <v>高松市香西本町476-1</v>
       </c>
       <c r="F96" t="str">
-        <v>４階と屋上の駐車場部分</v>
+        <v>２階</v>
       </c>
       <c r="G96" t="str">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="H96" t="str">
         <v>香西</v>
@@ -2897,25 +2897,25 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B97" t="str">
-        <v>34.34682444</v>
+        <v>34.34290278</v>
       </c>
       <c r="C97" t="str">
-        <v>133.99622</v>
+        <v>134.0037278</v>
       </c>
       <c r="D97" t="str">
-        <v>香西コミュニティセンター</v>
+        <v>パーラーグランド香西</v>
       </c>
       <c r="E97" t="str">
-        <v>高松市香西本町476-1</v>
+        <v>高松市香西南町378-1</v>
       </c>
       <c r="F97" t="str">
-        <v>２階</v>
+        <v>立体駐車場の２階から屋上まで</v>
       </c>
       <c r="G97" t="str">
-        <v>100</v>
+        <v>3600</v>
       </c>
       <c r="H97" t="str">
         <v>香西</v>
@@ -2923,25 +2923,25 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B98" t="str">
-        <v>34.34290278</v>
+        <v>34.34211111</v>
       </c>
       <c r="C98" t="str">
-        <v>134.0037278</v>
+        <v>134.0007281</v>
       </c>
       <c r="D98" t="str">
-        <v>パーラーグランド香西</v>
+        <v>ふれあい福祉センター勝賀</v>
       </c>
       <c r="E98" t="str">
-        <v>高松市香西南町378-1</v>
+        <v>高松市香西南町476-1</v>
       </c>
       <c r="F98" t="str">
-        <v>立体駐車場の２階から屋上まで</v>
+        <v>２階</v>
       </c>
       <c r="G98" t="str">
-        <v>3600</v>
+        <v>100</v>
       </c>
       <c r="H98" t="str">
         <v>香西</v>
@@ -2949,22 +2949,22 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B99" t="str">
-        <v>34.34211111</v>
+        <v>34.33905028</v>
       </c>
       <c r="C99" t="str">
-        <v>134.0007281</v>
+        <v>133.9978061</v>
       </c>
       <c r="D99" t="str">
-        <v>ふれあい福祉センター勝賀</v>
+        <v>勝賀中学校</v>
       </c>
       <c r="E99" t="str">
-        <v>高松市香西南町476-1</v>
+        <v>高松市香西南町565</v>
       </c>
       <c r="F99" t="str">
-        <v>２階</v>
+        <v>校舎</v>
       </c>
       <c r="G99" t="str">
         <v>100</v>
@@ -2975,25 +2975,25 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B100" t="str">
-        <v>34.33905028</v>
+        <v>34.34546083</v>
       </c>
       <c r="C100" t="str">
-        <v>133.9978061</v>
+        <v>133.9979003</v>
       </c>
       <c r="D100" t="str">
-        <v>勝賀中学校</v>
+        <v>香西小学校</v>
       </c>
       <c r="E100" t="str">
-        <v>高松市香西南町565</v>
+        <v>高松市香西南町703-1</v>
       </c>
       <c r="F100" t="str">
         <v>校舎</v>
       </c>
       <c r="G100" t="str">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H100" t="str">
         <v>香西</v>
@@ -3001,25 +3001,25 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B101" t="str">
-        <v>34.34546083</v>
+        <v>34.35634</v>
       </c>
       <c r="C101" t="str">
-        <v>133.9979003</v>
+        <v>133.9888564</v>
       </c>
       <c r="D101" t="str">
-        <v>香西小学校</v>
+        <v>特別養護老人ホームシオンの丘ホーム</v>
       </c>
       <c r="E101" t="str">
-        <v>高松市香西南町703-1</v>
+        <v>高松市香西北町260</v>
       </c>
       <c r="F101" t="str">
-        <v>校舎</v>
+        <v>４階テラス部分と屋上</v>
       </c>
       <c r="G101" t="str">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H101" t="str">
         <v>香西</v>
@@ -3027,25 +3027,25 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B102" t="str">
-        <v>34.35634</v>
+        <v>34.34254472</v>
       </c>
       <c r="C102" t="str">
-        <v>133.9888564</v>
+        <v>134.007305</v>
       </c>
       <c r="D102" t="str">
-        <v>特別養護老人ホームシオンの丘ホーム</v>
+        <v>ＤＣＭダイキ香西店</v>
       </c>
       <c r="E102" t="str">
-        <v>高松市香西北町260</v>
+        <v>高松市香西東町350-1</v>
       </c>
       <c r="F102" t="str">
-        <v>４階テラス部分と屋上</v>
+        <v>屋上駐車場</v>
       </c>
       <c r="G102" t="str">
-        <v>250</v>
+        <v>800</v>
       </c>
       <c r="H102" t="str">
         <v>香西</v>
@@ -3053,51 +3053,51 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B103" t="str">
-        <v>34.34254472</v>
+        <v>34.35712528</v>
       </c>
       <c r="C103" t="str">
-        <v>134.007305</v>
+        <v>133.9559758</v>
       </c>
       <c r="D103" t="str">
-        <v>ＤＣＭダイキ香西店</v>
+        <v>下笠居小学校</v>
       </c>
       <c r="E103" t="str">
-        <v>高松市香西東町350-1</v>
+        <v>高松市生島町345</v>
       </c>
       <c r="F103" t="str">
-        <v>屋上駐車場</v>
+        <v>体育館</v>
       </c>
       <c r="G103" t="str">
-        <v>800</v>
+        <v>550</v>
       </c>
       <c r="H103" t="str">
-        <v>香西</v>
+        <v>下笠居</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B104" t="str">
-        <v>34.35712528</v>
+        <v>34.35870861</v>
       </c>
       <c r="C104" t="str">
-        <v>133.9559758</v>
+        <v>133.9687664</v>
       </c>
       <c r="D104" t="str">
-        <v>下笠居小学校</v>
+        <v>下笠居コミュニティセンター</v>
       </c>
       <c r="E104" t="str">
-        <v>高松市生島町345</v>
+        <v>高松市生島町353-1</v>
       </c>
       <c r="F104" t="str">
-        <v>体育館</v>
+        <v>施設内</v>
       </c>
       <c r="G104" t="str">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="H104" t="str">
         <v>下笠居</v>
@@ -3105,25 +3105,25 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B105" t="str">
-        <v>34.35870861</v>
+        <v>34.35771139</v>
       </c>
       <c r="C105" t="str">
-        <v>133.9687664</v>
+        <v>133.9666417</v>
       </c>
       <c r="D105" t="str">
-        <v>下笠居コミュニティセンター</v>
+        <v>下笠居中学校</v>
       </c>
       <c r="E105" t="str">
-        <v>高松市生島町353-1</v>
+        <v>高松市生島町372-1</v>
       </c>
       <c r="F105" t="str">
-        <v>施設内</v>
+        <v>体育館</v>
       </c>
       <c r="G105" t="str">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="H105" t="str">
         <v>下笠居</v>
@@ -3131,51 +3131,51 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B106" t="str">
-        <v>34.35771139</v>
+        <v>34.33324056</v>
       </c>
       <c r="C106" t="str">
-        <v>133.9666417</v>
+        <v>134.1535814</v>
       </c>
       <c r="D106" t="str">
-        <v>下笠居中学校</v>
+        <v>牟礼南小学校</v>
       </c>
       <c r="E106" t="str">
-        <v>高松市生島町372-1</v>
+        <v>高松市牟礼町大町1115-1</v>
       </c>
       <c r="F106" t="str">
-        <v>体育館</v>
+        <v>校舎</v>
       </c>
       <c r="G106" t="str">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="H106" t="str">
-        <v>下笠居</v>
+        <v>牟礼</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B107" t="str">
-        <v>34.33324056</v>
+        <v>34.33351</v>
       </c>
       <c r="C107" t="str">
-        <v>134.1535814</v>
+        <v>134.1567117</v>
       </c>
       <c r="D107" t="str">
-        <v>牟礼南小学校</v>
+        <v>道の駅源平の里むれ</v>
       </c>
       <c r="E107" t="str">
-        <v>高松市牟礼町大町1115-1</v>
+        <v>高松市牟礼町原631-7</v>
       </c>
       <c r="F107" t="str">
-        <v>校舎</v>
+        <v>物産館および真念堂</v>
       </c>
       <c r="G107" t="str">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H107" t="str">
         <v>牟礼</v>
@@ -3183,45 +3183,45 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B108" t="str">
-        <v>34.33351</v>
+        <v>34.38324278</v>
       </c>
       <c r="C108" t="str">
-        <v>134.1567117</v>
+        <v>134.1307706</v>
       </c>
       <c r="D108" t="str">
-        <v>道の駅源平の里むれ</v>
+        <v>庵治中学校</v>
       </c>
       <c r="E108" t="str">
-        <v>高松市牟礼町原631-7</v>
+        <v>高松市庵治町691-1</v>
       </c>
       <c r="F108" t="str">
-        <v>物産館および真念堂</v>
+        <v>校舎</v>
       </c>
       <c r="G108" t="str">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H108" t="str">
-        <v>牟礼</v>
+        <v>庵治</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B109" t="str">
-        <v>34.38324278</v>
+        <v>34.3844425</v>
       </c>
       <c r="C109" t="str">
-        <v>134.1307706</v>
+        <v>134.1318539</v>
       </c>
       <c r="D109" t="str">
-        <v>庵治中学校</v>
+        <v>庵治小学校</v>
       </c>
       <c r="E109" t="str">
-        <v>高松市庵治町691-1</v>
+        <v>高松市庵治町790-1</v>
       </c>
       <c r="F109" t="str">
         <v>校舎</v>
@@ -3235,25 +3235,25 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B110" t="str">
-        <v>34.3844425</v>
+        <v>34.3853175</v>
       </c>
       <c r="C110" t="str">
-        <v>134.1318539</v>
+        <v>134.1299483</v>
       </c>
       <c r="D110" t="str">
-        <v>庵治小学校</v>
+        <v>庵治コミュニティセンター</v>
       </c>
       <c r="E110" t="str">
-        <v>高松市庵治町790-1</v>
+        <v>高松市庵治町888-1</v>
       </c>
       <c r="F110" t="str">
-        <v>校舎</v>
+        <v>２階</v>
       </c>
       <c r="G110" t="str">
-        <v>100</v>
+        <v>850</v>
       </c>
       <c r="H110" t="str">
         <v>庵治</v>
@@ -3261,25 +3261,25 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B111" t="str">
-        <v>34.3853175</v>
+        <v>34.38328139</v>
       </c>
       <c r="C111" t="str">
-        <v>134.1299483</v>
+        <v>134.1249322</v>
       </c>
       <c r="D111" t="str">
-        <v>庵治コミュニティセンター</v>
+        <v>庵治やすらぎ会館</v>
       </c>
       <c r="E111" t="str">
-        <v>高松市庵治町888-1</v>
+        <v>高松市庵治町6392-14</v>
       </c>
       <c r="F111" t="str">
         <v>２階</v>
       </c>
       <c r="G111" t="str">
-        <v>850</v>
+        <v>50</v>
       </c>
       <c r="H111" t="str">
         <v>庵治</v>
@@ -3287,22 +3287,22 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B112" t="str">
-        <v>34.38328139</v>
+        <v>34.38463139</v>
       </c>
       <c r="C112" t="str">
-        <v>134.1249322</v>
+        <v>134.1264239</v>
       </c>
       <c r="D112" t="str">
-        <v>庵治やすらぎ会館</v>
+        <v>庵治支所</v>
       </c>
       <c r="E112" t="str">
-        <v>高松市庵治町6392-14</v>
+        <v>高松市庵治町6393-5</v>
       </c>
       <c r="F112" t="str">
-        <v>２階</v>
+        <v>議会棟</v>
       </c>
       <c r="G112" t="str">
         <v>50</v>
@@ -3313,59 +3313,33 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B113" t="str">
-        <v>34.38463139</v>
+        <v>34.388357</v>
       </c>
       <c r="C113" t="str">
-        <v>134.1264239</v>
+        <v>134.129479</v>
       </c>
       <c r="D113" t="str">
-        <v>庵治支所</v>
+        <v>庵治保健センター（ほっとぴあん）</v>
       </c>
       <c r="E113" t="str">
-        <v>高松市庵治町6393-5</v>
+        <v>高松市庵治町978</v>
       </c>
       <c r="F113" t="str">
-        <v>議会棟</v>
+        <v>バルコニー部分</v>
       </c>
       <c r="G113" t="str">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="H113" t="str">
         <v>庵治</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="str">
-        <v>114</v>
-      </c>
-      <c r="B114" t="str">
-        <v>34.388357</v>
-      </c>
-      <c r="C114" t="str">
-        <v>134.129479</v>
-      </c>
-      <c r="D114" t="str">
-        <v>庵治保健センター（ほっとぴあん）</v>
-      </c>
-      <c r="E114" t="str">
-        <v>高松市庵治町978</v>
-      </c>
-      <c r="F114" t="str">
-        <v>バルコニー部分</v>
-      </c>
-      <c r="G114" t="str">
-        <v>200</v>
-      </c>
-      <c r="H114" t="str">
-        <v>庵治</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H114"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H113"/>
   </ignoredErrors>
 </worksheet>
 </file>